--- a/考研/考研日记/考研日记.xlsx
+++ b/考研/考研日记/考研日记.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21431" windowHeight="10020"/>
+    <workbookView windowWidth="21383" windowHeight="10020"/>
   </bookViews>
   <sheets>
     <sheet name="考研日记" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>考研日记</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>有暑期课</t>
+  </si>
+  <si>
+    <t>高数：乐经良P7-10</t>
   </si>
 </sst>
 </file>
@@ -693,12 +696,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1048,607 +1048,609 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" ht="17.4" spans="1:9">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>44747</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>44748</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5" t="s">
+      <c r="H4" s="4"/>
+      <c r="I4" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>44749</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>44750</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>44751</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>44752</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>44753</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>44754</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>44755</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>44756</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>44757</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>44758</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="4">
+      <c r="A15" s="3">
         <v>44759</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>44760</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="4">
+      <c r="A17" s="3">
         <v>44761</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="4">
+      <c r="A18" s="3">
         <v>44762</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="4">
+      <c r="A19" s="3">
         <v>44763</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="4">
+      <c r="A20" s="3">
         <v>44764</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="4">
+      <c r="A21" s="3">
         <v>44765</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="4">
+      <c r="A22" s="3">
         <v>44766</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="4">
+      <c r="A23" s="3">
         <v>44767</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="4">
+      <c r="A24" s="3">
         <v>44768</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="4">
+      <c r="A25" s="3">
         <v>44769</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="4">
+      <c r="A26" s="3">
         <v>44770</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="4">
+      <c r="A27" s="3">
         <v>44771</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="4">
+      <c r="A28" s="3">
         <v>44772</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="4">
+      <c r="A29" s="3">
         <v>44773</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="4">
+      <c r="A30" s="3">
         <v>44774</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="4">
+      <c r="A31" s="3">
         <v>44775</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="4">
+      <c r="A32" s="3">
         <v>44776</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="4">
+      <c r="A33" s="3">
         <v>44777</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="4">
+      <c r="A34" s="3">
         <v>44778</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="4">
+      <c r="A35" s="3">
         <v>44779</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="4">
+      <c r="A36" s="3">
         <v>44780</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="4">
+      <c r="A37" s="3">
         <v>44781</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="4">
+      <c r="A38" s="3">
         <v>44782</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="4">
+      <c r="A39" s="3">
         <v>44783</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="4">
+      <c r="A40" s="3">
         <v>44784</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="4">
+      <c r="A41" s="3">
         <v>44785</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="4">
+      <c r="A42" s="3">
         <v>44786</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="4">
+      <c r="A43" s="3">
         <v>44787</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="4">
+      <c r="A44" s="3">
         <v>44788</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="4">
+      <c r="A45" s="3">
         <v>44789</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="4">
+      <c r="A46" s="3">
         <v>44790</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="4">
+      <c r="A47" s="3">
         <v>44791</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="4">
+      <c r="A48" s="3">
         <v>44792</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="4">
+      <c r="A49" s="3">
         <v>44793</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="4">
+      <c r="A50" s="3">
         <v>44794</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="4">
+      <c r="A51" s="3">
         <v>44795</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="4">
+      <c r="A52" s="3">
         <v>44796</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="4">
+      <c r="A53" s="3">
         <v>44797</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="4">
+      <c r="A54" s="3">
         <v>44798</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="4">
+      <c r="A55" s="3">
         <v>44799</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="4">
+      <c r="A56" s="3">
         <v>44800</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="4">
+      <c r="A57" s="3">
         <v>44801</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="4">
+      <c r="A58" s="3">
         <v>44802</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="4">
+      <c r="A59" s="3">
         <v>44803</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="4">
+      <c r="A60" s="3">
         <v>44804</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="4">
+      <c r="A61" s="3">
         <v>44805</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="4">
+      <c r="A62" s="3">
         <v>44806</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="4">
+      <c r="A63" s="3">
         <v>44807</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="4">
+      <c r="A64" s="3">
         <v>44808</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="4">
+      <c r="A65" s="3">
         <v>44809</v>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="4">
+      <c r="A66" s="3">
         <v>44810</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="4">
+      <c r="A67" s="3">
         <v>44811</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="4">
+      <c r="A68" s="3">
         <v>44812</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="4">
+      <c r="A69" s="3">
         <v>44813</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="4">
+      <c r="A70" s="3">
         <v>44814</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="4">
+      <c r="A71" s="3">
         <v>44815</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="4">
+      <c r="A72" s="3">
         <v>44816</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="4">
+      <c r="A73" s="3">
         <v>44817</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="4">
+      <c r="A74" s="3">
         <v>44818</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="4">
+      <c r="A75" s="3">
         <v>44819</v>
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="4">
+      <c r="A76" s="3">
         <v>44820</v>
       </c>
     </row>

--- a/考研/考研日记/考研日记.xlsx
+++ b/考研/考研日记/考研日记.xlsx
@@ -4,17 +4,18 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21383" windowHeight="10020"/>
+    <workbookView windowWidth="21431" windowHeight="10020"/>
   </bookViews>
   <sheets>
     <sheet name="考研日记" sheetId="1" r:id="rId1"/>
+    <sheet name="链接" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>考研日记</t>
   </si>
@@ -46,13 +47,13 @@
     <t>备注</t>
   </si>
   <si>
-    <t>高数：乐经良P1</t>
+    <t>高数：乐经良(171)P1</t>
   </si>
   <si>
     <t>查询部分考研信息</t>
   </si>
   <si>
-    <t>高数：乐经良P2-6</t>
+    <t>高数：乐经良(171)P2-6</t>
   </si>
   <si>
     <t>8h</t>
@@ -64,7 +65,40 @@
     <t>有暑期课</t>
   </si>
   <si>
-    <t>高数：乐经良P7-10</t>
+    <t>高数：乐经良(171)P7-10</t>
+  </si>
+  <si>
+    <t>高数：乐经良(171)P11-12</t>
+  </si>
+  <si>
+    <t>考研核心（List1）</t>
+  </si>
+  <si>
+    <t>摆烂</t>
+  </si>
+  <si>
+    <t>高数：乐经良(171)P11-12
+概率论：余炳森基础(32)P1-3</t>
+  </si>
+  <si>
+    <t>考研核心（List2）</t>
+  </si>
+  <si>
+    <t>高数：乐经良(171)P11-12
+线代：汤家凤基础（27）P1-2
+概率论：余炳森基础(32)P4-</t>
+  </si>
+  <si>
+    <t>2023考研数学-汤家凤线代基础班</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Gt4y1H7PN</t>
+  </si>
+  <si>
+    <t>2023考研数学余炳森基础概率（最新完整版）</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1WL4y1F7t1</t>
   </si>
 </sst>
 </file>
@@ -86,6 +120,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="20"/>
       <color theme="1"/>
@@ -133,14 +175,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -554,10 +588,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -566,31 +600,31 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -611,13 +645,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
@@ -629,10 +663,10 @@
     <xf numFmtId="0" fontId="17" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -647,70 +681,76 @@
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1034,7 +1074,7 @@
   <dimension ref="A1:I76"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="19.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="38.2222222222222" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="24.2222222222222" customWidth="1"/>
     <col min="5" max="5" width="18.2222222222222" customWidth="1"/>
@@ -1045,612 +1085,607 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.8" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" ht="17.4" spans="1:9">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="3">
+      <c r="A3" s="4">
         <v>44747</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="3">
+      <c r="A4" s="4">
         <v>44748</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4" t="s">
+      <c r="H4" s="5"/>
+      <c r="I4" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="3">
+      <c r="A5" s="4">
         <v>44749</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="3">
+      <c r="A6" s="4">
         <v>44750</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="3">
+      <c r="B6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" ht="28.8" spans="1:9">
+      <c r="A7" s="4">
         <v>44751</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="3">
+      <c r="B7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" ht="43.2" spans="1:9">
+      <c r="A8" s="4">
         <v>44752</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="B8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="3">
+      <c r="A9" s="4">
         <v>44753</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="3">
+      <c r="A10" s="4">
         <v>44754</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="3">
+      <c r="A11" s="4">
         <v>44755</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="3">
+      <c r="A12" s="4">
         <v>44756</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="3">
+      <c r="A13" s="4">
         <v>44757</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="3">
+      <c r="A14" s="4">
         <v>44758</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="3">
+      <c r="A15" s="4">
         <v>44759</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="3">
+      <c r="A16" s="4">
         <v>44760</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="3">
+      <c r="A17" s="4">
         <v>44761</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="3">
+      <c r="A18" s="4">
         <v>44762</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="3">
+      <c r="A19" s="4">
         <v>44763</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="3">
+      <c r="A20" s="4">
         <v>44764</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="3">
+      <c r="A21" s="4">
         <v>44765</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="3">
+      <c r="A22" s="4">
         <v>44766</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="3">
+      <c r="A23" s="4">
         <v>44767</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="3">
+      <c r="A24" s="4">
         <v>44768</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="3">
+      <c r="A25" s="4">
         <v>44769</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="3">
+      <c r="A26" s="4">
         <v>44770</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="3">
+      <c r="A27" s="4">
         <v>44771</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="3">
+      <c r="A28" s="4">
         <v>44772</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="3">
+      <c r="A29" s="4">
         <v>44773</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="3">
+      <c r="A30" s="4">
         <v>44774</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="3">
+      <c r="A31" s="4">
         <v>44775</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="3">
+      <c r="A32" s="4">
         <v>44776</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="3">
+      <c r="A33" s="4">
         <v>44777</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="3">
+      <c r="A34" s="4">
         <v>44778</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="3">
+      <c r="A35" s="4">
         <v>44779</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="3">
+      <c r="A36" s="4">
         <v>44780</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="3">
+      <c r="A37" s="4">
         <v>44781</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="3">
+      <c r="A38" s="4">
         <v>44782</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="3">
+      <c r="A39" s="4">
         <v>44783</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="3">
+      <c r="A40" s="4">
         <v>44784</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="3">
+      <c r="A41" s="4">
         <v>44785</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="3">
+      <c r="A42" s="4">
         <v>44786</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="3">
+      <c r="A43" s="4">
         <v>44787</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="3">
+      <c r="A44" s="4">
         <v>44788</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="3">
+      <c r="A45" s="4">
         <v>44789</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="3">
+      <c r="A46" s="4">
         <v>44790</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="3">
+      <c r="A47" s="4">
         <v>44791</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="3">
+      <c r="A48" s="4">
         <v>44792</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="3">
+      <c r="A49" s="4">
         <v>44793</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="3">
+      <c r="A50" s="4">
         <v>44794</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="3">
+      <c r="A51" s="4">
         <v>44795</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="3">
+      <c r="A52" s="4">
         <v>44796</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="3">
+      <c r="A53" s="4">
         <v>44797</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="3">
+      <c r="A54" s="4">
         <v>44798</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="3">
+      <c r="A55" s="4">
         <v>44799</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="3">
+      <c r="A56" s="4">
         <v>44800</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="3">
+      <c r="A57" s="4">
         <v>44801</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="3">
+      <c r="A58" s="4">
         <v>44802</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="3">
+      <c r="A59" s="4">
         <v>44803</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="3">
+      <c r="A60" s="4">
         <v>44804</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="3">
+      <c r="A61" s="4">
         <v>44805</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="3">
+      <c r="A62" s="4">
         <v>44806</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="3">
+      <c r="A63" s="4">
         <v>44807</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="3">
+      <c r="A64" s="4">
         <v>44808</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="3">
+      <c r="A65" s="4">
         <v>44809</v>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="3">
+      <c r="A66" s="4">
         <v>44810</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="3">
+      <c r="A67" s="4">
         <v>44811</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="3">
+      <c r="A68" s="4">
         <v>44812</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="3">
+      <c r="A69" s="4">
         <v>44813</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="3">
+      <c r="A70" s="4">
         <v>44814</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="3">
+      <c r="A71" s="4">
         <v>44815</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="3">
+      <c r="A72" s="4">
         <v>44816</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="3">
+      <c r="A73" s="4">
         <v>44817</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="3">
+      <c r="A74" s="4">
         <v>44818</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="3">
+      <c r="A75" s="4">
         <v>44819</v>
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="3">
+      <c r="A76" s="4">
         <v>44820</v>
       </c>
     </row>
@@ -1661,4 +1696,40 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A2:B3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="46.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="45.5555555555556" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.bilibili.com/video/BV1Gt4y1H7PN"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://www.bilibili.com/video/BV1WL4y1F7t1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/考研/考研日记/考研日记.xlsx
+++ b/考研/考研日记/考研日记.xlsx
@@ -9,13 +9,14 @@
   <sheets>
     <sheet name="考研日记" sheetId="1" r:id="rId1"/>
     <sheet name="链接" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>考研日记</t>
   </si>
@@ -84,9 +85,83 @@
     <t>考研核心（List2）</t>
   </si>
   <si>
-    <t>高数：乐经良(171)P11-12
-线代：汤家凤基础（27）P1-2
-概率论：余炳森基础(32)P4-</t>
+    <t>线代：汤家凤基础（27）P1-2
+概率论：余炳森基础(32)P4</t>
+  </si>
+  <si>
+    <t>线代：汤家凤基础（27）P3-5
+概率论：余炳森基础(32)P5-7</t>
+  </si>
+  <si>
+    <t>一直在写安卓传感器应用</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)P1-2
+线代：汤家凤基础（27）P6-7</t>
+  </si>
+  <si>
+    <t>还是摆烂</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)P3
+线代：汤家凤基础（27）P8-9
+概率论：余炳森基础(32)P8-9</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)P4-5</t>
+  </si>
+  <si>
+    <t>考研核心（List3-4）</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)P6</t>
+  </si>
+  <si>
+    <t>考研核心（List5-6）</t>
+  </si>
+  <si>
+    <t>好像啥也没干</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)P7-9</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)P10-11
+概率论：余炳森基础(32)P8-11(复习)</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)P12
+概率论：余炳森基础(32)P12-15</t>
+  </si>
+  <si>
+    <t>徐涛强化：马原（32）P1</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)复习
+概率论：余炳森基础(32)P16-18</t>
+  </si>
+  <si>
+    <t>考研核心（List7-8）</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)P
+线代：汤家凤基础（27）P10-13
+概率论：余炳森基础(32)P19</t>
+  </si>
+  <si>
+    <t>考研核心（List9）</t>
+  </si>
+  <si>
+    <t>徐涛强化：马原（32）P2</t>
+  </si>
+  <si>
+    <t>10h+</t>
+  </si>
+  <si>
+    <t>2023考研数学 武老师高数基础+强化</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV17L4y1w7wY</t>
   </si>
   <si>
     <t>2023考研数学-汤家凤线代基础班</t>
@@ -98,7 +173,7 @@
     <t>2023考研数学余炳森基础概率（最新完整版）</t>
   </si>
   <si>
-    <t>https://www.bilibili.com/video/BV1WL4y1F7t1</t>
+    <t>https://www.bilibili.com/video/BV1934y1p7Dm</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1152,7 @@
     <col min="2" max="2" width="38.2222222222222" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="24.2222222222222" customWidth="1"/>
-    <col min="5" max="5" width="18.2222222222222" customWidth="1"/>
+    <col min="5" max="5" width="30.3333333333333" customWidth="1"/>
     <col min="6" max="6" width="20.2222222222222" customWidth="1"/>
     <col min="7" max="7" width="20.8888888888889" customWidth="1"/>
     <col min="8" max="8" width="23.3333333333333" customWidth="1"/>
@@ -1215,7 +1290,7 @@
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
     </row>
-    <row r="8" ht="43.2" spans="1:9">
+    <row r="8" ht="28.8" spans="1:9">
       <c r="A8" s="4">
         <v>44752</v>
       </c>
@@ -1230,9 +1305,12 @@
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" ht="28.8" spans="1:9">
       <c r="A9" s="4">
         <v>44753</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1240,23 +1318,33 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="I9" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" ht="28.8" spans="1:9">
       <c r="A10" s="4">
         <v>44754</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" ht="43.2" spans="1:9">
       <c r="A11" s="4">
         <v>44755</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -1270,7 +1358,12 @@
       <c r="A12" s="4">
         <v>44756</v>
       </c>
-      <c r="C12" s="5"/>
+      <c r="B12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -1282,7 +1375,12 @@
       <c r="A13" s="4">
         <v>44757</v>
       </c>
-      <c r="C13" s="5"/>
+      <c r="B13" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -1293,6 +1391,9 @@
     <row r="14" spans="1:9">
       <c r="A14" s="4">
         <v>44758</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -1306,6 +1407,9 @@
       <c r="A15" s="4">
         <v>44759</v>
       </c>
+      <c r="B15" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -1314,9 +1418,12 @@
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" ht="28.8" spans="1:9">
       <c r="A16" s="4">
         <v>44760</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -1326,23 +1433,33 @@
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" ht="28.8" spans="1:9">
       <c r="A17" s="4">
         <v>44761</v>
       </c>
+      <c r="B17" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" ht="28.8" spans="1:9">
       <c r="A18" s="4">
         <v>44762</v>
       </c>
-      <c r="C18" s="5"/>
+      <c r="B18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -1350,14 +1467,23 @@
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" ht="43.2" spans="1:9">
       <c r="A19" s="4">
         <v>44763</v>
       </c>
-      <c r="C19" s="5"/>
+      <c r="B19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="E19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -1701,35 +1827,57 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:B3"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="46.8888888888889" customWidth="1"/>
-    <col min="2" max="2" width="45.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="56.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="45.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="C3" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" display="https://www.bilibili.com/video/BV1Gt4y1H7PN"/>
-    <hyperlink ref="B3" r:id="rId2" display="https://www.bilibili.com/video/BV1WL4y1F7t1"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://www.bilibili.com/video/BV1934y1p7Dm" tooltip="https://www.bilibili.com/video/BV1934y1p7Dm"/>
+    <hyperlink ref="B1" r:id="rId3" display="https://www.bilibili.com/video/BV17L4y1w7wY"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/考研/考研日记/考研日记.xlsx
+++ b/考研/考研日记/考研日记.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>考研日记</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>考研核心（List2）</t>
+  </si>
+  <si>
+    <t>感觉乐经良太多了，来不及</t>
   </si>
   <si>
     <t>线代：汤家凤基础（27）P1-2
@@ -144,7 +147,7 @@
     <t>考研核心（List7-8）</t>
   </si>
   <si>
-    <t>高数：武忠祥基础(24)P
+    <t>高数：武忠祥基础(24)复习
 线代：汤家凤基础（27）P10-13
 概率论：余炳森基础(32)P19</t>
   </si>
@@ -156,6 +159,46 @@
   </si>
   <si>
     <t>10h+</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)复习
+概率论：余炳森基础(32)P20-22</t>
+  </si>
+  <si>
+    <t>考研核心（List10）</t>
+  </si>
+  <si>
+    <t>下午晚上在研究综合设计大作业</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)复习
+概率论：余炳森基础(32)P23</t>
+  </si>
+  <si>
+    <t>有点摆烂</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)复习
+线代：汤家凤基础（27）P14-15
+概率论：余炳森基础(32)P24-25</t>
+  </si>
+  <si>
+    <t>考研核心（List11）</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)复习
+线代：汤家凤基础（27）P16-17
+概率论：余炳森基础(32)P26</t>
+  </si>
+  <si>
+    <t>徐涛强化：马原（32）P3</t>
+  </si>
+  <si>
+    <t>一整天安卓啥也没写出来，傻逼了
+找到好教程可太重要了</t>
+  </si>
+  <si>
+    <t>上午+下午安卓写出来了，继续复习考研</t>
   </si>
   <si>
     <t>2023考研数学 武老师高数基础+强化</t>
@@ -805,7 +848,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -826,6 +869,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1146,7 +1192,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I177"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="38.2222222222222" customWidth="1"/>
@@ -1155,8 +1201,8 @@
     <col min="5" max="5" width="30.3333333333333" customWidth="1"/>
     <col min="6" max="6" width="20.2222222222222" customWidth="1"/>
     <col min="7" max="7" width="20.8888888888889" customWidth="1"/>
-    <col min="8" max="8" width="23.3333333333333" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="8" max="8" width="30.2222222222222" customWidth="1"/>
+    <col min="9" max="9" width="31.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.8" spans="1:9">
@@ -1287,7 +1333,9 @@
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
+      <c r="H7" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="I7" s="5"/>
     </row>
     <row r="8" ht="28.8" spans="1:9">
@@ -1295,7 +1343,7 @@
         <v>44752</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1310,7 +1358,7 @@
         <v>44753</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1319,7 +1367,7 @@
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" ht="28.8" spans="1:9">
@@ -1327,7 +1375,7 @@
         <v>44754</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -1335,7 +1383,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I10" s="5"/>
     </row>
@@ -1344,7 +1392,7 @@
         <v>44755</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -1359,10 +1407,10 @@
         <v>44756</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -1376,10 +1424,10 @@
         <v>44757</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -1393,7 +1441,7 @@
         <v>44758</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -1408,7 +1456,7 @@
         <v>44759</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -1423,7 +1471,7 @@
         <v>44760</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -1438,12 +1486,12 @@
         <v>44761</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -1455,10 +1503,10 @@
         <v>44762</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -1472,37 +1520,47 @@
         <v>44763</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" ht="28.8" spans="1:9">
       <c r="A20" s="4">
         <v>44764</v>
       </c>
-      <c r="C20" s="5"/>
+      <c r="B20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="I20" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" ht="28.8" spans="1:9">
       <c r="A21" s="4">
         <v>44765</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -1510,13 +1568,20 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="I21" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" ht="43.2" spans="1:9">
       <c r="A22" s="4">
         <v>44766</v>
       </c>
-      <c r="C22" s="5"/>
+      <c r="B22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -1528,6 +1593,7 @@
       <c r="A23" s="4">
         <v>44767</v>
       </c>
+      <c r="B23" s="6"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
@@ -1536,17 +1602,24 @@
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" ht="43.2" spans="1:9">
       <c r="A24" s="4">
         <v>44768</v>
       </c>
+      <c r="B24" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
+      <c r="E24" s="5" t="s">
+        <v>52</v>
+      </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
+      <c r="I24" s="7" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="4">
@@ -1558,7 +1631,9 @@
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
+      <c r="I25" s="5" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="4">
@@ -1813,6 +1888,511 @@
     <row r="76" spans="1:1">
       <c r="A76" s="4">
         <v>44820</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="4">
+        <v>44821</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="4">
+        <v>44822</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="4">
+        <v>44823</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="4">
+        <v>44824</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="4">
+        <v>44825</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="4">
+        <v>44826</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="4">
+        <v>44827</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="4">
+        <v>44828</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="4">
+        <v>44829</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="4">
+        <v>44830</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="4">
+        <v>44831</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="4">
+        <v>44832</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="4">
+        <v>44833</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="4">
+        <v>44834</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="4">
+        <v>44835</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="4">
+        <v>44836</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="4">
+        <v>44837</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="4">
+        <v>44838</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="4">
+        <v>44839</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="4">
+        <v>44840</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="4">
+        <v>44841</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="4">
+        <v>44842</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="4">
+        <v>44843</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="4">
+        <v>44844</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="4">
+        <v>44845</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="4">
+        <v>44846</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="4">
+        <v>44847</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="4">
+        <v>44848</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="4">
+        <v>44849</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="4">
+        <v>44850</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="4">
+        <v>44851</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="4">
+        <v>44852</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="4">
+        <v>44853</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="4">
+        <v>44854</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="4">
+        <v>44855</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="4">
+        <v>44856</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="4">
+        <v>44857</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="4">
+        <v>44858</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="4">
+        <v>44859</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="4">
+        <v>44860</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="4">
+        <v>44861</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="4">
+        <v>44862</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="4">
+        <v>44863</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="4">
+        <v>44864</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="4">
+        <v>44865</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="4">
+        <v>44866</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="4">
+        <v>44867</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="4">
+        <v>44868</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="4">
+        <v>44869</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="4">
+        <v>44870</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="4">
+        <v>44871</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="4">
+        <v>44872</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="4">
+        <v>44873</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="4">
+        <v>44874</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="4">
+        <v>44875</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="4">
+        <v>44876</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="4">
+        <v>44877</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="4">
+        <v>44878</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="4">
+        <v>44879</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="4">
+        <v>44880</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="4">
+        <v>44881</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="4">
+        <v>44882</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="4">
+        <v>44883</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="4">
+        <v>44884</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="4">
+        <v>44885</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="4">
+        <v>44886</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="4">
+        <v>44887</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="4">
+        <v>44888</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="4">
+        <v>44889</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="4">
+        <v>44890</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="4">
+        <v>44891</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="4">
+        <v>44892</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="4">
+        <v>44893</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="4">
+        <v>44894</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="4">
+        <v>44895</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="4">
+        <v>44896</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="4">
+        <v>44897</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="4">
+        <v>44898</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="4">
+        <v>44899</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="4">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="4">
+        <v>44901</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="4">
+        <v>44902</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="4">
+        <v>44903</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="4">
+        <v>44904</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="4">
+        <v>44905</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="4">
+        <v>44906</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="4">
+        <v>44907</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="4">
+        <v>44908</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="4">
+        <v>44909</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="4">
+        <v>44910</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="4">
+        <v>44911</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="4">
+        <v>44912</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="4">
+        <v>44913</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="4">
+        <v>44914</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="4">
+        <v>44915</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="4">
+        <v>44916</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="4">
+        <v>44917</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="4">
+        <v>44918</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="4">
+        <v>44919</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="4">
+        <v>44920</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="4">
+        <v>44921</v>
       </c>
     </row>
   </sheetData>
@@ -1837,26 +2417,26 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C3" s="1"/>
     </row>

--- a/考研/考研日记/考研日记.xlsx
+++ b/考研/考研日记/考研日记.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>考研日记</t>
   </si>
@@ -186,6 +186,9 @@
     <t>考研核心（List11）</t>
   </si>
   <si>
+    <t>应该是摆烂了，不记得干了啥</t>
+  </si>
+  <si>
     <t>高数：武忠祥基础(24)复习
 线代：汤家凤基础（27）P16-17
 概率论：余炳森基础(32)P26</t>
@@ -198,7 +201,40 @@
 找到好教程可太重要了</t>
   </si>
   <si>
-    <t>上午+下午安卓写出来了，继续复习考研</t>
+    <t>高数：武忠祥基础(24)复习
+线代：汤家凤基础（27）P18-19
+概率论：余炳森基础(32)P27</t>
+  </si>
+  <si>
+    <t>考研核心（List12-13）</t>
+  </si>
+  <si>
+    <t>徐涛强化：马原（32）P4</t>
+  </si>
+  <si>
+    <t>上午+下午安卓写出来了，
+继续复习考研</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)复习到终值定理
+线代：汤家凤基础（27）P20-21
+概率论：余炳森基础(32)复习+P28-30</t>
+  </si>
+  <si>
+    <t>考研核心（List14）</t>
+  </si>
+  <si>
+    <t>卢京潮（80）：P1</t>
+  </si>
+  <si>
+    <t>徐涛强化：马原（32）P5</t>
+  </si>
+  <si>
+    <t>8h+</t>
+  </si>
+  <si>
+    <t>要加速了，效率要提高。
+争取400+。</t>
   </si>
   <si>
     <t>2023考研数学 武老师高数基础+强化</t>
@@ -217,6 +253,116 @@
   </si>
   <si>
     <t>https://www.bilibili.com/video/BV1934y1p7Dm</t>
+  </si>
+  <si>
+    <t>经验帖</t>
+  </si>
+  <si>
+    <t>记上海交通大学自动化考研经历</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/43641310</t>
+  </si>
+  <si>
+    <t>上海交通大学自动化考研经验与教训</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/178436302</t>
+  </si>
+  <si>
+    <t>22上交816控制专硕考研</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/489936535</t>
+  </si>
+  <si>
+    <t>复试</t>
+  </si>
+  <si>
+    <t>微机 c++ 控制理论</t>
+  </si>
+  <si>
+    <t>我去年的复试英语是面试时问了一个英语口语问题，自我介绍，兴趣啊对交大校园的感觉这类，听力占20分，好几道六级原题。</t>
+  </si>
+  <si>
+    <t>考口语和听力，口语主要是面试让你用英文回答问题</t>
+  </si>
+  <si>
+    <r>
+      <t>所以</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF121212"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF121212"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>专业课</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF121212"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>150+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF121212"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数学</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF121212"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>120+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF121212"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>英语</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF121212"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>70</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF121212"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，政治你只要考60分，就400分了</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -229,7 +375,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,6 +390,32 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.25"/>
+      <color rgb="FF121212"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.25"/>
+      <color rgb="FF444444"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF121212"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -285,14 +457,6 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -396,6 +560,12 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF121212"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -706,10 +876,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -718,19 +888,19 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -742,123 +912,138 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -872,6 +1057,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1199,1205 +1387,1233 @@
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="24.2222222222222" customWidth="1"/>
     <col min="5" max="5" width="30.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="20.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="20.2222222222222" style="6" customWidth="1"/>
     <col min="7" max="7" width="20.8888888888889" customWidth="1"/>
     <col min="8" max="8" width="30.2222222222222" customWidth="1"/>
     <col min="9" max="9" width="31.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.8" spans="1:9">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
     </row>
     <row r="2" ht="17.4" spans="1:9">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="4">
+      <c r="A3" s="9">
         <v>44747</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="4">
+      <c r="A4" s="9">
         <v>44748</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5" t="s">
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5" t="s">
+      <c r="H4" s="10"/>
+      <c r="I4" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="4">
+      <c r="A5" s="9">
         <v>44749</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="4">
+      <c r="A6" s="9">
         <v>44750</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5" t="s">
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" ht="28.8" spans="1:9">
-      <c r="A7" s="4">
+      <c r="A7" s="9">
         <v>44751</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="5"/>
+      <c r="I7" s="10"/>
     </row>
     <row r="8" ht="28.8" spans="1:9">
-      <c r="A8" s="4">
+      <c r="A8" s="9">
         <v>44752</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
     </row>
     <row r="9" ht="28.8" spans="1:9">
-      <c r="A9" s="4">
+      <c r="A9" s="9">
         <v>44753</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5" t="s">
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" ht="28.8" spans="1:9">
-      <c r="A10" s="4">
+      <c r="A10" s="9">
         <v>44754</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5" t="s">
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="5"/>
+      <c r="I10" s="10"/>
     </row>
     <row r="11" ht="43.2" spans="1:9">
-      <c r="A11" s="4">
+      <c r="A11" s="9">
         <v>44755</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="4">
+      <c r="A12" s="9">
         <v>44756</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="4">
+      <c r="A13" s="9">
         <v>44757</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="4">
+      <c r="A14" s="9">
         <v>44758</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="4">
+      <c r="A15" s="9">
         <v>44759</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
     </row>
     <row r="16" ht="28.8" spans="1:9">
-      <c r="A16" s="4">
+      <c r="A16" s="9">
         <v>44760</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
     </row>
     <row r="17" ht="28.8" spans="1:9">
-      <c r="A17" s="4">
+      <c r="A17" s="9">
         <v>44761</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5" t="s">
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
     </row>
     <row r="18" ht="28.8" spans="1:9">
-      <c r="A18" s="4">
+      <c r="A18" s="9">
         <v>44762</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
     </row>
     <row r="19" ht="43.2" spans="1:9">
-      <c r="A19" s="4">
+      <c r="A19" s="9">
         <v>44763</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5" t="s">
+      <c r="D19" s="10"/>
+      <c r="E19" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
     </row>
     <row r="20" ht="28.8" spans="1:9">
-      <c r="A20" s="4">
+      <c r="A20" s="9">
         <v>44764</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5" t="s">
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="21" ht="28.8" spans="1:9">
-      <c r="A21" s="4">
+      <c r="A21" s="9">
         <v>44765</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5" t="s">
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="22" ht="43.2" spans="1:9">
-      <c r="A22" s="4">
+      <c r="A22" s="9">
         <v>44766</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="4">
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:9">
+      <c r="A23" s="9">
         <v>44767</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
+      <c r="B23" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
     </row>
     <row r="24" ht="43.2" spans="1:9">
-      <c r="A24" s="4">
+      <c r="A24" s="9">
         <v>44768</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5" t="s">
+      <c r="B24" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="7" t="s">
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="4">
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" ht="43.2" spans="1:9">
+      <c r="A25" s="9">
         <v>44769</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="4">
+      <c r="B25" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" ht="43.2" spans="1:8">
+      <c r="A26" s="9">
         <v>44770</v>
       </c>
+      <c r="B26" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="4">
+      <c r="A27" s="9">
         <v>44771</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="4">
+      <c r="A28" s="9">
         <v>44772</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="4">
+      <c r="A29" s="9">
         <v>44773</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="4">
+      <c r="A30" s="9">
         <v>44774</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="4">
+      <c r="A31" s="9">
         <v>44775</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="4">
+      <c r="A32" s="9">
         <v>44776</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="4">
+      <c r="A33" s="9">
         <v>44777</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="4">
+      <c r="A34" s="9">
         <v>44778</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="4">
+      <c r="A35" s="9">
         <v>44779</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="4">
+      <c r="A36" s="9">
         <v>44780</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="4">
+      <c r="A37" s="9">
         <v>44781</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="4">
+      <c r="A38" s="9">
         <v>44782</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="4">
+      <c r="A39" s="9">
         <v>44783</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="4">
+      <c r="A40" s="9">
         <v>44784</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="4">
+      <c r="A41" s="9">
         <v>44785</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="4">
+      <c r="A42" s="9">
         <v>44786</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="4">
+      <c r="A43" s="9">
         <v>44787</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="4">
+      <c r="A44" s="9">
         <v>44788</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="4">
+      <c r="A45" s="9">
         <v>44789</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="4">
+      <c r="A46" s="9">
         <v>44790</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="4">
+      <c r="A47" s="9">
         <v>44791</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="4">
+      <c r="A48" s="9">
         <v>44792</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="4">
+      <c r="A49" s="9">
         <v>44793</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="4">
+      <c r="A50" s="9">
         <v>44794</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="4">
+      <c r="A51" s="9">
         <v>44795</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="4">
+      <c r="A52" s="9">
         <v>44796</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="4">
+      <c r="A53" s="9">
         <v>44797</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="4">
+      <c r="A54" s="9">
         <v>44798</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="4">
+      <c r="A55" s="9">
         <v>44799</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="4">
+      <c r="A56" s="9">
         <v>44800</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="4">
+      <c r="A57" s="9">
         <v>44801</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="4">
+      <c r="A58" s="9">
         <v>44802</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="4">
+      <c r="A59" s="9">
         <v>44803</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="4">
+      <c r="A60" s="9">
         <v>44804</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="4">
+      <c r="A61" s="9">
         <v>44805</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="4">
+      <c r="A62" s="9">
         <v>44806</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="4">
+      <c r="A63" s="9">
         <v>44807</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="4">
+      <c r="A64" s="9">
         <v>44808</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="4">
+      <c r="A65" s="9">
         <v>44809</v>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="4">
+      <c r="A66" s="9">
         <v>44810</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="4">
+      <c r="A67" s="9">
         <v>44811</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="4">
+      <c r="A68" s="9">
         <v>44812</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="4">
+      <c r="A69" s="9">
         <v>44813</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="4">
+      <c r="A70" s="9">
         <v>44814</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="4">
+      <c r="A71" s="9">
         <v>44815</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="4">
+      <c r="A72" s="9">
         <v>44816</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="4">
+      <c r="A73" s="9">
         <v>44817</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="4">
+      <c r="A74" s="9">
         <v>44818</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="4">
+      <c r="A75" s="9">
         <v>44819</v>
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="4">
+      <c r="A76" s="9">
         <v>44820</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="4">
+      <c r="A77" s="9">
         <v>44821</v>
       </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="4">
+      <c r="A78" s="9">
         <v>44822</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="4">
+      <c r="A79" s="9">
         <v>44823</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="4">
+      <c r="A80" s="9">
         <v>44824</v>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="4">
+      <c r="A81" s="9">
         <v>44825</v>
       </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="4">
+      <c r="A82" s="9">
         <v>44826</v>
       </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="4">
+      <c r="A83" s="9">
         <v>44827</v>
       </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="4">
+      <c r="A84" s="9">
         <v>44828</v>
       </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="4">
+      <c r="A85" s="9">
         <v>44829</v>
       </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="4">
+      <c r="A86" s="9">
         <v>44830</v>
       </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="4">
+      <c r="A87" s="9">
         <v>44831</v>
       </c>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="4">
+      <c r="A88" s="9">
         <v>44832</v>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="4">
+      <c r="A89" s="9">
         <v>44833</v>
       </c>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="4">
+      <c r="A90" s="9">
         <v>44834</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="4">
+      <c r="A91" s="9">
         <v>44835</v>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="4">
+      <c r="A92" s="9">
         <v>44836</v>
       </c>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="4">
+      <c r="A93" s="9">
         <v>44837</v>
       </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="4">
+      <c r="A94" s="9">
         <v>44838</v>
       </c>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="4">
+      <c r="A95" s="9">
         <v>44839</v>
       </c>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="4">
+      <c r="A96" s="9">
         <v>44840</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="4">
+      <c r="A97" s="9">
         <v>44841</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="4">
+      <c r="A98" s="9">
         <v>44842</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="4">
+      <c r="A99" s="9">
         <v>44843</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="4">
+      <c r="A100" s="9">
         <v>44844</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="4">
+      <c r="A101" s="9">
         <v>44845</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="4">
+      <c r="A102" s="9">
         <v>44846</v>
       </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="4">
+      <c r="A103" s="9">
         <v>44847</v>
       </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="4">
+      <c r="A104" s="9">
         <v>44848</v>
       </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="4">
+      <c r="A105" s="9">
         <v>44849</v>
       </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="4">
+      <c r="A106" s="9">
         <v>44850</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="4">
+      <c r="A107" s="9">
         <v>44851</v>
       </c>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="4">
+      <c r="A108" s="9">
         <v>44852</v>
       </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="4">
+      <c r="A109" s="9">
         <v>44853</v>
       </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="4">
+      <c r="A110" s="9">
         <v>44854</v>
       </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="4">
+      <c r="A111" s="9">
         <v>44855</v>
       </c>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="4">
+      <c r="A112" s="9">
         <v>44856</v>
       </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="4">
+      <c r="A113" s="9">
         <v>44857</v>
       </c>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="4">
+      <c r="A114" s="9">
         <v>44858</v>
       </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="4">
+      <c r="A115" s="9">
         <v>44859</v>
       </c>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="4">
+      <c r="A116" s="9">
         <v>44860</v>
       </c>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="4">
+      <c r="A117" s="9">
         <v>44861</v>
       </c>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="4">
+      <c r="A118" s="9">
         <v>44862</v>
       </c>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="4">
+      <c r="A119" s="9">
         <v>44863</v>
       </c>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="4">
+      <c r="A120" s="9">
         <v>44864</v>
       </c>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="4">
+      <c r="A121" s="9">
         <v>44865</v>
       </c>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="4">
+      <c r="A122" s="9">
         <v>44866</v>
       </c>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="4">
+      <c r="A123" s="9">
         <v>44867</v>
       </c>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="4">
+      <c r="A124" s="9">
         <v>44868</v>
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="4">
+      <c r="A125" s="9">
         <v>44869</v>
       </c>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="4">
+      <c r="A126" s="9">
         <v>44870</v>
       </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="4">
+      <c r="A127" s="9">
         <v>44871</v>
       </c>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="4">
+      <c r="A128" s="9">
         <v>44872</v>
       </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="4">
+      <c r="A129" s="9">
         <v>44873</v>
       </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="4">
+      <c r="A130" s="9">
         <v>44874</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="4">
+      <c r="A131" s="9">
         <v>44875</v>
       </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="4">
+      <c r="A132" s="9">
         <v>44876</v>
       </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="4">
+      <c r="A133" s="9">
         <v>44877</v>
       </c>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" s="4">
+      <c r="A134" s="9">
         <v>44878</v>
       </c>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="4">
+      <c r="A135" s="9">
         <v>44879</v>
       </c>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="4">
+      <c r="A136" s="9">
         <v>44880</v>
       </c>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="4">
+      <c r="A137" s="9">
         <v>44881</v>
       </c>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="4">
+      <c r="A138" s="9">
         <v>44882</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="4">
+      <c r="A139" s="9">
         <v>44883</v>
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="4">
+      <c r="A140" s="9">
         <v>44884</v>
       </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="4">
+      <c r="A141" s="9">
         <v>44885</v>
       </c>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="4">
+      <c r="A142" s="9">
         <v>44886</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="4">
+      <c r="A143" s="9">
         <v>44887</v>
       </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="4">
+      <c r="A144" s="9">
         <v>44888</v>
       </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="4">
+      <c r="A145" s="9">
         <v>44889</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="4">
+      <c r="A146" s="9">
         <v>44890</v>
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="4">
+      <c r="A147" s="9">
         <v>44891</v>
       </c>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="4">
+      <c r="A148" s="9">
         <v>44892</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="4">
+      <c r="A149" s="9">
         <v>44893</v>
       </c>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="4">
+      <c r="A150" s="9">
         <v>44894</v>
       </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="4">
+      <c r="A151" s="9">
         <v>44895</v>
       </c>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="4">
+      <c r="A152" s="9">
         <v>44896</v>
       </c>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="4">
+      <c r="A153" s="9">
         <v>44897</v>
       </c>
     </row>
     <row r="154" spans="1:1">
-      <c r="A154" s="4">
+      <c r="A154" s="9">
         <v>44898</v>
       </c>
     </row>
     <row r="155" spans="1:1">
-      <c r="A155" s="4">
+      <c r="A155" s="9">
         <v>44899</v>
       </c>
     </row>
     <row r="156" spans="1:1">
-      <c r="A156" s="4">
+      <c r="A156" s="9">
         <v>44900</v>
       </c>
     </row>
     <row r="157" spans="1:1">
-      <c r="A157" s="4">
+      <c r="A157" s="9">
         <v>44901</v>
       </c>
     </row>
     <row r="158" spans="1:1">
-      <c r="A158" s="4">
+      <c r="A158" s="9">
         <v>44902</v>
       </c>
     </row>
     <row r="159" spans="1:1">
-      <c r="A159" s="4">
+      <c r="A159" s="9">
         <v>44903</v>
       </c>
     </row>
     <row r="160" spans="1:1">
-      <c r="A160" s="4">
+      <c r="A160" s="9">
         <v>44904</v>
       </c>
     </row>
     <row r="161" spans="1:1">
-      <c r="A161" s="4">
+      <c r="A161" s="9">
         <v>44905</v>
       </c>
     </row>
     <row r="162" spans="1:1">
-      <c r="A162" s="4">
+      <c r="A162" s="9">
         <v>44906</v>
       </c>
     </row>
     <row r="163" spans="1:1">
-      <c r="A163" s="4">
+      <c r="A163" s="9">
         <v>44907</v>
       </c>
     </row>
     <row r="164" spans="1:1">
-      <c r="A164" s="4">
+      <c r="A164" s="9">
         <v>44908</v>
       </c>
     </row>
     <row r="165" spans="1:1">
-      <c r="A165" s="4">
+      <c r="A165" s="9">
         <v>44909</v>
       </c>
     </row>
     <row r="166" spans="1:1">
-      <c r="A166" s="4">
+      <c r="A166" s="9">
         <v>44910</v>
       </c>
     </row>
     <row r="167" spans="1:1">
-      <c r="A167" s="4">
+      <c r="A167" s="9">
         <v>44911</v>
       </c>
     </row>
     <row r="168" spans="1:1">
-      <c r="A168" s="4">
+      <c r="A168" s="9">
         <v>44912</v>
       </c>
     </row>
     <row r="169" spans="1:1">
-      <c r="A169" s="4">
+      <c r="A169" s="9">
         <v>44913</v>
       </c>
     </row>
     <row r="170" spans="1:1">
-      <c r="A170" s="4">
+      <c r="A170" s="9">
         <v>44914</v>
       </c>
     </row>
     <row r="171" spans="1:1">
-      <c r="A171" s="4">
+      <c r="A171" s="9">
         <v>44915</v>
       </c>
     </row>
     <row r="172" spans="1:1">
-      <c r="A172" s="4">
+      <c r="A172" s="9">
         <v>44916</v>
       </c>
     </row>
     <row r="173" spans="1:1">
-      <c r="A173" s="4">
+      <c r="A173" s="9">
         <v>44917</v>
       </c>
     </row>
     <row r="174" spans="1:1">
-      <c r="A174" s="4">
+      <c r="A174" s="9">
         <v>44918</v>
       </c>
     </row>
     <row r="175" spans="1:1">
-      <c r="A175" s="4">
+      <c r="A175" s="9">
         <v>44919</v>
       </c>
     </row>
     <row r="176" spans="1:1">
-      <c r="A176" s="4">
+      <c r="A176" s="9">
         <v>44920</v>
       </c>
     </row>
     <row r="177" spans="1:1">
-      <c r="A177" s="4">
+      <c r="A177" s="9">
         <v>44921</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B23:I23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2407,44 +2623,102 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="2"/>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="46.8888888888889" customWidth="1"/>
     <col min="2" max="2" width="56.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="45.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="80.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C3" s="1"/>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" ht="30" spans="1:1">
+      <c r="A19" s="5" t="s">
+        <v>82</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" display="https://www.bilibili.com/video/BV1Gt4y1H7PN"/>
     <hyperlink ref="B3" r:id="rId2" display="https://www.bilibili.com/video/BV1934y1p7Dm" tooltip="https://www.bilibili.com/video/BV1934y1p7Dm"/>
     <hyperlink ref="B1" r:id="rId3" display="https://www.bilibili.com/video/BV17L4y1w7wY"/>
+    <hyperlink ref="B10" r:id="rId4" display="https://zhuanlan.zhihu.com/p/489936535"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/考研/考研日记/考研日记.xlsx
+++ b/考研/考研日记/考研日记.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21431" windowHeight="10020"/>
+    <workbookView windowWidth="21383" windowHeight="9947"/>
   </bookViews>
   <sheets>
     <sheet name="考研日记" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="143">
   <si>
     <t>考研日记</t>
   </si>
@@ -218,13 +218,13 @@
   <si>
     <t>高数：武忠祥基础(24)复习到终值定理
 线代：汤家凤基础（27）P20-21
-概率论：余炳森基础(32)复习+P28-30</t>
+概率论：余炳森基础(32)P28-30</t>
   </si>
   <si>
     <t>考研核心（List14）</t>
   </si>
   <si>
-    <t>卢京潮（80）：P1</t>
+    <t>自控卢京潮（80）：P1</t>
   </si>
   <si>
     <t>徐涛强化：马原（32）P5</t>
@@ -237,6 +237,166 @@
 争取400+。</t>
   </si>
   <si>
+    <t>高数：武忠祥基础(24)
+线代：汤家凤基础（27）P22-24
+概率论：余炳森基础(32)P31-32（完结）+练习题</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P2</t>
+  </si>
+  <si>
+    <t>徐涛强化：马原（32）P6</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)复习</t>
+  </si>
+  <si>
+    <t>不背单词*180</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P3-5</t>
+  </si>
+  <si>
+    <t>10h</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)复习
+线代：汤家凤强化（目前只有10）P1
+概率论：余炳森强化(27)P1+复习</t>
+  </si>
+  <si>
+    <t>背了</t>
+  </si>
+  <si>
+    <t>徐涛强化：马原（32）P7</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)13-14
+线代：汤家凤强化（目前只有10）P2-3
+概率论：余炳森强化(27)P1+复习</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)14-17
+概率论：余炳森强化(27)P2-3</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)18-19
+线代：汤家凤强化（目前只有10）P4
+概率论：余炳森强化(27)P4</t>
+  </si>
+  <si>
+    <t>7h</t>
+  </si>
+  <si>
+    <t>有点多</t>
+  </si>
+  <si>
+    <t>明天开始看英语</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)20</t>
+  </si>
+  <si>
+    <t>单词+阅读</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)22
+线代：汤家凤强化（目前只有10）P5-7</t>
+  </si>
+  <si>
+    <t>单词+阅读+作文学习</t>
+  </si>
+  <si>
+    <t>高数：武忠祥基础(24)第一遍完结</t>
+  </si>
+  <si>
+    <t>高数660：1-22</t>
+  </si>
+  <si>
+    <t>高数660：23-41</t>
+  </si>
+  <si>
+    <t>高数660：426-438
+高数：武忠祥强化（23）P1
+概率论：余炳森强化(27)P4-5</t>
+  </si>
+  <si>
+    <t>高数660：
+概率论：余炳森强化(27)P6-7</t>
+  </si>
+  <si>
+    <t>高数660：
+高数：武忠祥强化（23）P2
+概率论：余炳森强化(27)P8-10</t>
+  </si>
+  <si>
+    <t>徐涛强化：马原（32）P1（复习）</t>
+  </si>
+  <si>
+    <t>明天开始看专业课</t>
+  </si>
+  <si>
+    <t>高数660：
+高数：武忠祥强化（23）P3</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P5-6
+拉普拉斯变换</t>
+  </si>
+  <si>
+    <t>徐涛强化：马原（32）P2-5（复习）</t>
+  </si>
+  <si>
+    <t>明天加大力度，优点感觉了</t>
+  </si>
+  <si>
+    <t>高数660：
+高数：武忠祥强化（23）P4</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P7-10
+拉普拉斯变换</t>
+  </si>
+  <si>
+    <t>徐涛强化：马原（32）P6-7（复习）</t>
+  </si>
+  <si>
+    <t>高数660：
+高数：武忠祥强化（23）复习
+概率论：余炳森强化(27)P11</t>
+  </si>
+  <si>
+    <t>徐涛强化：马原（32）P8-9</t>
+  </si>
+  <si>
+    <t>单词+阅读(2005阅读*2)</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P11-14</t>
+  </si>
+  <si>
+    <t>徐涛强化：马原（32）P10</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P15-16</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P17-18
+现控中南大学（16）：P1</t>
+  </si>
+  <si>
+    <t>写小学期大作业</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P19</t>
+  </si>
+  <si>
+    <t>单词+阅读(完型*2)</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P20-21</t>
+  </si>
+  <si>
     <t>2023考研数学 武老师高数基础+强化</t>
   </si>
   <si>
@@ -252,7 +412,49 @@
     <t>2023考研数学余炳森基础概率（最新完整版）</t>
   </si>
   <si>
-    <t>https://www.bilibili.com/video/BV1934y1p7Dm</t>
+    <t>https://www.bilibili.com/video/BV1kB4y1t7Pt</t>
+  </si>
+  <si>
+    <t>武忠祥基础+23强化-2023考研数学武忠祥高等数学（最全）</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1GN4y1T7o6</t>
+  </si>
+  <si>
+    <t>23考研数学汤家凤线代强化（强化班）</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV17d4y1K7AC</t>
+  </si>
+  <si>
+    <t>【2023余炳森】概率论与数理统计强化班【完整版】</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1XG4y1e78a</t>
+  </si>
+  <si>
+    <t>【已完结】23李永乐660题逐题讲解1~190题【含数1、2、3】</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1jY4y1i7qT</t>
+  </si>
+  <si>
+    <t>现代控制理论-中南大学</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1gA4y1Z7GA</t>
+  </si>
+  <si>
+    <t>《自动控制原理》西北工业大学 卢京潮 （去黑边）</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1ZJ411c757</t>
+  </si>
+  <si>
+    <t>2023考研英语田静英一英二句句真研完整版</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1WT411A798</t>
   </si>
   <si>
     <t>经验帖</t>
@@ -289,6 +491,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF121212"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>所以</t>
     </r>
     <r>
@@ -1018,7 +1226,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1050,16 +1258,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1383,10 +1585,10 @@
   <dimension ref="A1:I177"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="38.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="47" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="24.2222222222222" customWidth="1"/>
-    <col min="5" max="5" width="30.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="30.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="35.2222222222222" customWidth="1"/>
     <col min="6" max="6" width="20.2222222222222" style="6" customWidth="1"/>
     <col min="7" max="7" width="20.8888888888889" customWidth="1"/>
     <col min="8" max="8" width="30.2222222222222" customWidth="1"/>
@@ -1442,13 +1644,12 @@
       <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1459,17 +1660,17 @@
       <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10" t="s">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10" t="s">
+      <c r="H4" s="6"/>
+      <c r="I4" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1480,30 +1681,28 @@
       <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="9">
         <v>44750</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10" t="s">
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1511,50 +1710,47 @@
       <c r="A7" s="9">
         <v>44751</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10" t="s">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="10"/>
+      <c r="I7" s="6"/>
     </row>
     <row r="8" ht="28.8" spans="1:9">
       <c r="A8" s="9">
         <v>44752</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
     </row>
     <row r="9" ht="28.8" spans="1:9">
       <c r="A9" s="9">
         <v>44753</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1562,67 +1758,63 @@
       <c r="A10" s="9">
         <v>44754</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="10"/>
+      <c r="I10" s="6"/>
     </row>
     <row r="11" ht="43.2" spans="1:9">
       <c r="A11" s="9">
         <v>44755</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="9">
         <v>44756</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="9">
         <v>44757</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="9">
@@ -1631,115 +1823,109 @@
       <c r="B14" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="9">
         <v>44759</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
     </row>
     <row r="16" ht="28.8" spans="1:9">
       <c r="A16" s="9">
         <v>44760</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
     </row>
     <row r="17" ht="28.8" spans="1:9">
       <c r="A17" s="9">
         <v>44761</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10" t="s">
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
     </row>
     <row r="18" ht="28.8" spans="1:9">
       <c r="A18" s="9">
         <v>44762</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
     </row>
     <row r="19" ht="43.2" spans="1:9">
       <c r="A19" s="9">
         <v>44763</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10" t="s">
+      <c r="D19" s="6"/>
+      <c r="E19" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
     </row>
     <row r="20" ht="28.8" spans="1:9">
       <c r="A20" s="9">
         <v>44764</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10" t="s">
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1747,16 +1933,15 @@
       <c r="A21" s="9">
         <v>44765</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10" t="s">
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1764,50 +1949,48 @@
       <c r="A22" s="9">
         <v>44766</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:9">
       <c r="A23" s="9">
         <v>44767</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
     </row>
     <row r="24" ht="43.2" spans="1:9">
       <c r="A24" s="9">
         <v>44768</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10" t="s">
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="12" t="s">
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="11" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1815,20 +1998,19 @@
       <c r="A25" s="9">
         <v>44769</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10" t="s">
+      <c r="D25" s="6"/>
+      <c r="E25" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="12" t="s">
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="11" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1836,28 +2018,37 @@
       <c r="A26" s="9">
         <v>44770</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="6" t="s">
         <v>60</v>
       </c>
       <c r="D26" t="s">
         <v>61</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="6" t="s">
         <v>62</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="H26" s="13" t="s">
+      <c r="H26" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" ht="43.2" spans="1:5">
       <c r="A27" s="9">
         <v>44771</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:1">
@@ -1870,114 +2061,274 @@
         <v>44773</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:6">
       <c r="A30" s="9">
         <v>44774</v>
       </c>
-    </row>
-    <row r="31" spans="1:1">
+      <c r="B30" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" ht="43.2" spans="1:6">
       <c r="A31" s="9">
         <v>44775</v>
       </c>
-    </row>
-    <row r="32" spans="1:1">
+      <c r="B31" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" ht="43.2" spans="1:2">
       <c r="A32" s="9">
         <v>44776</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
+      <c r="B32" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" ht="28.8" spans="1:3">
       <c r="A33" s="9">
         <v>44777</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" ht="43.2" spans="1:8">
       <c r="A34" s="9">
         <v>44778</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G34" t="s">
+        <v>79</v>
+      </c>
+      <c r="H34" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" s="9">
         <v>44779</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" ht="28.8" spans="1:6">
       <c r="A36" s="9">
         <v>44780</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" t="s">
+        <v>84</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" s="9">
         <v>44781</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" s="10"/>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" s="9">
         <v>44782</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" s="9">
         <v>44783</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" s="9">
         <v>44784</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" ht="43.2" spans="1:2">
       <c r="A41" s="9">
         <v>44785</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="B41" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" ht="28.8" spans="1:2">
       <c r="A42" s="9">
         <v>44786</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
+      <c r="B42" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" ht="43.2" spans="1:8">
       <c r="A43" s="9">
         <v>44787</v>
       </c>
-    </row>
-    <row r="44" spans="1:1">
+      <c r="B43" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" ht="28.8" spans="1:8">
       <c r="A44" s="9">
         <v>44788</v>
       </c>
-    </row>
-    <row r="45" spans="1:1">
+      <c r="B44" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" t="s">
+        <v>82</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H44" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" ht="28.8" spans="1:5">
       <c r="A45" s="9">
         <v>44789</v>
       </c>
-    </row>
-    <row r="46" spans="1:1">
+      <c r="B45" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" ht="43.2" spans="1:5">
       <c r="A46" s="9">
         <v>44790</v>
       </c>
-    </row>
-    <row r="47" spans="1:1">
+      <c r="B46" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C46" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" s="9">
         <v>44791</v>
       </c>
-    </row>
-    <row r="48" spans="1:1">
+      <c r="C47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48" s="9">
         <v>44792</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
+      <c r="D48" s="10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="49" ht="28.8" spans="1:8">
       <c r="A49" s="9">
         <v>44793</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="D49" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H49" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="9">
         <v>44794</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="D50" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H50" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="9">
         <v>44795</v>
+      </c>
+      <c r="C51" t="s">
+        <v>109</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H51" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -2623,102 +2974,170 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="46.8888888888889" customWidth="1"/>
+    <col min="1" max="1" width="68.2222222222222" customWidth="1"/>
     <col min="2" max="2" width="56.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="80.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="58" customWidth="1"/>
+    <col min="4" max="4" width="50.2222222222222" customWidth="1"/>
+    <col min="5" max="5" width="13.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="C3" s="1"/>
     </row>
-    <row r="7" spans="1:1">
+    <row r="4" spans="2:3">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
+        <v>121</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="3:3">
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" spans="1:1">
+        <v>123</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" ht="30" spans="1:1">
-      <c r="A19" s="5" t="s">
-        <v>82</v>
+        <v>129</v>
+      </c>
+      <c r="B14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3">
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1" spans="1:1">
+      <c r="A35" s="5" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" display="https://www.bilibili.com/video/BV1Gt4y1H7PN"/>
-    <hyperlink ref="B3" r:id="rId2" display="https://www.bilibili.com/video/BV1934y1p7Dm" tooltip="https://www.bilibili.com/video/BV1934y1p7Dm"/>
-    <hyperlink ref="B1" r:id="rId3" display="https://www.bilibili.com/video/BV17L4y1w7wY"/>
-    <hyperlink ref="B10" r:id="rId4" display="https://zhuanlan.zhihu.com/p/489936535"/>
+    <hyperlink ref="B1" r:id="rId2" display="https://www.bilibili.com/video/BV17L4y1w7wY"/>
+    <hyperlink ref="B26" r:id="rId3" display="https://zhuanlan.zhihu.com/p/489936535"/>
+    <hyperlink ref="B7" r:id="rId4" display="https://www.bilibili.com/video/BV1XG4y1e78a"/>
+    <hyperlink ref="B5" r:id="rId5" display="https://www.bilibili.com/video/BV1GN4y1T7o6"/>
+    <hyperlink ref="B9" r:id="rId6" display="https://www.bilibili.com/video/BV1jY4y1i7qT" tooltip="https://www.bilibili.com/video/BV1jY4y1i7qT"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/考研/考研日记/考研日记.xlsx
+++ b/考研/考研日记/考研日记.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21383" windowHeight="9947"/>
+    <workbookView windowWidth="21383" windowHeight="9960"/>
   </bookViews>
   <sheets>
     <sheet name="考研日记" sheetId="1" r:id="rId1"/>
     <sheet name="链接" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="数学好题记录" sheetId="3" r:id="rId3"/>
+    <sheet name="考研英语作文" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="295">
   <si>
     <t>考研日记</t>
   </si>
@@ -347,7 +348,7 @@
     <t>徐涛强化：马原（32）P2-5（复习）</t>
   </si>
   <si>
-    <t>明天加大力度，优点感觉了</t>
+    <t>明天加大力度，有点感觉了</t>
   </si>
   <si>
     <t>高数660：
@@ -397,6 +398,487 @@
     <t>自控卢京潮（80）：P20-21</t>
   </si>
   <si>
+    <t>单词+阅读(阅读*3)</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P22-23</t>
+  </si>
+  <si>
+    <t>今天英语准确率还行，三篇只错一个，需要保持，英语作文最好也看起来，还有长难句，背单词</t>
+  </si>
+  <si>
+    <t>写小学期大作业，感谢yyr帮忙调通了一个bug
+jmzy跟我说要联系导师，否则就没机会了</t>
+  </si>
+  <si>
+    <t>高数660：
+线代：汤家凤强化（目前只有15）P1-2(复习)
+概率论：余炳森强化(27)P1-2(复习)</t>
+  </si>
+  <si>
+    <t>单词+阅读(阅读*2+完型)</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P24-26（到了根轨迹）</t>
+  </si>
+  <si>
+    <t>今天英语准确率也还行。选句填空错了一个。速度有点慢，应该下次提高些。
+自控有点生疏了，可能之前没学好。</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）复习
+线代：汤家凤强化（目前只有15）P3-4(复习)
+概率论：余炳森强化(24)P3-4(复习)</t>
+  </si>
+  <si>
+    <t>单词+阅读(阅读*4)</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P27-28</t>
+  </si>
+  <si>
+    <t>复习了一会</t>
+  </si>
+  <si>
+    <t>英语今天4篇一共错三个，需要改进，速度还行，一个小时不到。</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）复习
+线代：汤家凤强化（目前只有15）P5-6(复习)</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P29-30</t>
+  </si>
+  <si>
+    <t>完型错成sb，选句填空全队，阅读一篇错一个。感谢qyc讲解</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）复习，明天开新的
+线代：汤家凤强化（目前只有15）P7(复习)</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P31-32</t>
+  </si>
+  <si>
+    <t>英语还是错的多，理科有点学不进去很烦</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）P5
+严选题第一章1-20：准确率还行
+线代：汤家凤强化（目前只有15）P8-9</t>
+  </si>
+  <si>
+    <t>单词+阅读(阅读*3)
+恋词词组</t>
+  </si>
+  <si>
+    <t>复习拉普拉斯，新课看不进去</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）P6</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）P7-8</t>
+  </si>
+  <si>
+    <t>徐涛强化：史纲（21）P1-2</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）P9</t>
+  </si>
+  <si>
+    <t>徐涛强化：史纲（21）P3</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化复习第二章</t>
+  </si>
+  <si>
+    <t>苏一说了：马原（62）P1-2+肖1000相关</t>
+  </si>
+  <si>
+    <t>苏一说了：马原（62）P3+肖1000相关</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）P10</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）P11</t>
+  </si>
+  <si>
+    <t>苏一说了：马原（62）P4-5+肖1000相关</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）P12-13</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）P14-16</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P33</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P34-36</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P37-38</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P39-43
+现控中南（16）：P1-2</t>
+  </si>
+  <si>
+    <t>一点机器学习</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P44-46(46不全)
+自控卢京潮（80）：P47-48暂时跳过了
+现控中南（16）：P3-4</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P49-50(一半)</t>
+  </si>
+  <si>
+    <t>概率论：余炳森强化(27)P1(复习)</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P50-53(一半)
+现控中南（16）：P5</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P53</t>
+  </si>
+  <si>
+    <t>概率论：余炳森强化(27)P2-3(复习)</t>
+  </si>
+  <si>
+    <t>单词+阅读
+石磊鹏小作文01部分</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P54
+现控中南（16）：P6</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）复习
+概率论：余炳森强化(27)P4(复习)</t>
+  </si>
+  <si>
+    <t>单词+阅读
+石磊鹏小作文01一半</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P69-70
+现控中南（16）：P7</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）复习</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P71-72
+现控中南（16）：P8</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）P17-18(一半)</t>
+  </si>
+  <si>
+    <t>自控卢京潮（80）：P73-74
+现控中南（16）：P8</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）P18+整理</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）整理</t>
+  </si>
+  <si>
+    <t>跃点1-1-1——1-1-3、2-8-2</t>
+  </si>
+  <si>
+    <t>苏一说了：史纲（46）P1</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）P19</t>
+  </si>
+  <si>
+    <t>单词+阅读+翻译</t>
+  </si>
+  <si>
+    <t>跃点2-8-3——2-8-6</t>
+  </si>
+  <si>
+    <t>苏一说了：史纲（46）P2-4 + 肖1000配套</t>
+  </si>
+  <si>
+    <t>高数：第六章严选题（前半）</t>
+  </si>
+  <si>
+    <t>跃点2-1-0——2-1-5</t>
+  </si>
+  <si>
+    <t>苏一说了：史纲（46）P5-7 + 肖1000配套</t>
+  </si>
+  <si>
+    <t>概率论：余炳森强化(27)P5-6</t>
+  </si>
+  <si>
+    <t>跃点2-8-7——2-8-8(纯纯背诵，麻了)
+跃点2-8-9——2-8-10
+跃点2-1-6——2-1-7</t>
+  </si>
+  <si>
+    <t>苏一说了：史纲（46）P8-12 + 肖1000配套</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）P20+21一半
+线代：汤家凤强化（23）P1-3
+概率论：余炳森强化(27)P7-8</t>
+  </si>
+  <si>
+    <t>单词
+石磊鹏小作文01一大半</t>
+  </si>
+  <si>
+    <t>苏一说了：史纲（46）P13-16</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）P20+21一半
+线代：汤家凤强化（23）P4-5
+概率论：余炳森强化(27)P9-11</t>
+  </si>
+  <si>
+    <t>单词
+石磊鹏小作文01几乎全部</t>
+  </si>
+  <si>
+    <t>苏一说了：史纲（46）P17-18 + 肖1000配套</t>
+  </si>
+  <si>
+    <t>概率论：余炳森强化(27)P12-13
+线代：汤家凤强化（23）P6</t>
+  </si>
+  <si>
+    <t>苏一说了：史纲（46）P19-20</t>
+  </si>
+  <si>
+    <t>概率论：余炳森强化(27)P14-15
+线代：汤家凤强化（23）P7-8一半</t>
+  </si>
+  <si>
+    <t>线代：汤家凤强化（23）P8-10
+概率论：余炳森强化(27)P16-17
+高数：武忠祥强化（24）P21+22一半</t>
+  </si>
+  <si>
+    <t>苏一说了：史纲（46）P21-22</t>
+  </si>
+  <si>
+    <t>概率论：余炳森强化(27)P18-19+大数定律强化习题
+线代：汤家凤强化（23）P11-13
+高数：武忠祥复习</t>
+  </si>
+  <si>
+    <t>2010翻译（唐静）</t>
+  </si>
+  <si>
+    <t>跃点2-1-8</t>
+  </si>
+  <si>
+    <t>线代：汤家凤强化（23）P14-16
+概率论：余炳森强化(27)P20-22</t>
+  </si>
+  <si>
+    <t>作文词组</t>
+  </si>
+  <si>
+    <t>苏一说了：史纲（46）P23-26+肖1000之前欠的</t>
+  </si>
+  <si>
+    <t>概率论：余炳森强化(27)P23-24
+线代：汤家凤强化（23）P17一半
+高数：武忠祥第八章严选题</t>
+  </si>
+  <si>
+    <t>单词
+作文词组</t>
+  </si>
+  <si>
+    <t>苏一说了：史纲（46）P27-31+肖1000配套</t>
+  </si>
+  <si>
+    <t>概率论：余炳森强化(27)P25-27
+高数：武忠祥强化（24）P22-23</t>
+  </si>
+  <si>
+    <t>苏一说了：史纲（46）P32-37</t>
+  </si>
+  <si>
+    <t>线代：汤家凤强化（23）P17-19
+高数：武忠祥强化（24）P24</t>
+  </si>
+  <si>
+    <t>石磊鹏 大作文功能句1-3
+王江涛词组</t>
+  </si>
+  <si>
+    <t>苏一说了：史纲（46）P38-40+肖1000之前欠的</t>
+  </si>
+  <si>
+    <t>线代：汤家凤强化（23）P20-23</t>
+  </si>
+  <si>
+    <t>石磊鹏 大作文功能句4-37王江涛词组</t>
+  </si>
+  <si>
+    <t>苍盾小程序史纲第一章
+苏一说了：史纲（46）P41-46</t>
+  </si>
+  <si>
+    <t>跃点计算器+拉普拉斯变换+2-2-1——2-2-3</t>
+  </si>
+  <si>
+    <t>张修齐：马原（20）1-4</t>
+  </si>
+  <si>
+    <t>概率论：余炳森强化复习</t>
+  </si>
+  <si>
+    <t>王江涛词组</t>
+  </si>
+  <si>
+    <t>跃点2-2-4——2-2-11</t>
+  </si>
+  <si>
+    <t>张修齐：马原（20）5-6</t>
+  </si>
+  <si>
+    <t>王江涛词组+小作文书信类</t>
+  </si>
+  <si>
+    <t>跃点2-3-1——2-3-7&amp;2-8-1</t>
+  </si>
+  <si>
+    <t>张修齐：马原（20）7-9</t>
+  </si>
+  <si>
+    <t>线性代数辅导讲义严选题第一章
+概率论辅导讲义第一章</t>
+  </si>
+  <si>
+    <t>王江涛小作文各类+2005范文</t>
+  </si>
+  <si>
+    <t>跃点2-8-2——2-8-4</t>
+  </si>
+  <si>
+    <t>王江涛大作文各类</t>
+  </si>
+  <si>
+    <t>跃点2-8-5——2-8-8</t>
+  </si>
+  <si>
+    <t>肖1000唯物论做完，没订正</t>
+  </si>
+  <si>
+    <t>跃点2-8-9——2-8-13</t>
+  </si>
+  <si>
+    <t>订正一半</t>
+  </si>
+  <si>
+    <t>王江涛大作文
+小作文一篇</t>
+  </si>
+  <si>
+    <t>跃点2-8-14——2-8-21</t>
+  </si>
+  <si>
+    <t>张修齐：马原（20）10-11</t>
+  </si>
+  <si>
+    <t>线性代数复习</t>
+  </si>
+  <si>
+    <t>跃点2-8-22——2-8-26、2-3-8——2-3-10</t>
+  </si>
+  <si>
+    <t>线性代数+概率论复习</t>
+  </si>
+  <si>
+    <t>2005小作文+复习+单词</t>
+  </si>
+  <si>
+    <t>跃点2-3-8——2-3-18</t>
+  </si>
+  <si>
+    <t>发高烧</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）P1-3</t>
+  </si>
+  <si>
+    <t>跃点2-4-1——2-4-7</t>
+  </si>
+  <si>
+    <t>高数：武忠祥强化（24）P4-5+17堂课（19）P1的1/3</t>
+  </si>
+  <si>
+    <t>跃点2-5-1——2-5-7</t>
+  </si>
+  <si>
+    <t>张修齐：马原（20）12-13</t>
+  </si>
+  <si>
+    <t>跃点2-5-8——2-5-18</t>
+  </si>
+  <si>
+    <t>徐涛马原唯物史观</t>
+  </si>
+  <si>
+    <t>跃点2-5-19——2-5-20，2-6-1——2-6-4</t>
+  </si>
+  <si>
+    <t>跃点2-7-01——2-7-07</t>
+  </si>
+  <si>
+    <t>徐涛马原政经</t>
+  </si>
+  <si>
+    <t>单词</t>
+  </si>
+  <si>
+    <t>跃点2-7-08——2-7-15</t>
+  </si>
+  <si>
+    <t>王江涛英语大作文+单词</t>
+  </si>
+  <si>
+    <t>跃点3-1-0——3-1-5</t>
+  </si>
+  <si>
+    <t>徐涛马原政经垄断</t>
+  </si>
+  <si>
+    <t>徐涛马原over</t>
+  </si>
+  <si>
+    <t>2006小作文+2005大作文+2005翻译</t>
+  </si>
+  <si>
+    <t>2006大作文+2006翻译</t>
+  </si>
+  <si>
+    <t>跃点提高</t>
+  </si>
+  <si>
+    <t>冲刺背诵手册</t>
+  </si>
+  <si>
+    <t>线性代数+高等数学冲刺课</t>
+  </si>
+  <si>
+    <t>跃点频率校正</t>
+  </si>
+  <si>
     <t>2023考研数学 武老师高数基础+强化</t>
   </si>
   <si>
@@ -418,19 +900,16 @@
     <t>武忠祥基础+23强化-2023考研数学武忠祥高等数学（最全）</t>
   </si>
   <si>
-    <t>https://www.bilibili.com/video/BV1GN4y1T7o6</t>
-  </si>
-  <si>
     <t>23考研数学汤家凤线代强化（强化班）</t>
   </si>
   <si>
-    <t>https://www.bilibili.com/video/BV17d4y1K7AC</t>
+    <t>https://www.bilibili.com/video/BV1Ze4y1f7B6</t>
   </si>
   <si>
     <t>【2023余炳森】概率论与数理统计强化班【完整版】</t>
   </si>
   <si>
-    <t>https://www.bilibili.com/video/BV1XG4y1e78a</t>
+    <t>youtube</t>
   </si>
   <si>
     <t>【已完结】23李永乐660题逐题讲解1~190题【含数1、2、3】</t>
@@ -572,6 +1051,31 @@
       <t>，政治你只要考60分，就400分了</t>
     </r>
   </si>
+  <si>
+    <t>武忠祥严选题</t>
+  </si>
+  <si>
+    <t>第一章 函数、极限、连续</t>
+  </si>
+  <si>
+    <t>8（一题多解）、11（正规讨论）、18（这类题不太会，B站收藏夹）</t>
+  </si>
+  <si>
+    <t>图画作文</t>
+  </si>
+  <si>
+    <t>两人爬山</t>
+  </si>
+  <si>
+    <t>坚持</t>
+  </si>
+  <si>
+    <t>indomitable、invincible
+our only enemy is ourselves</t>
+  </si>
+  <si>
+    <t>应用文</t>
+  </si>
 </sst>
 </file>
 
@@ -583,9 +1087,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1084,10 +1596,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1096,34 +1608,31 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1135,133 +1644,142 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="10" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="10">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="10">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1582,1389 +2100,3256 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I177"/>
+  <dimension ref="A1:K177"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="47" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="30.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="35.2222222222222" customWidth="1"/>
-    <col min="6" max="6" width="20.2222222222222" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.2222222222222" customWidth="1"/>
+    <col min="4" max="4" width="39.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="44.1111111111111" customWidth="1"/>
+    <col min="6" max="6" width="20.2222222222222" style="8" customWidth="1"/>
     <col min="7" max="7" width="20.8888888888889" customWidth="1"/>
-    <col min="8" max="8" width="30.2222222222222" customWidth="1"/>
+    <col min="8" max="8" width="36" customWidth="1"/>
     <col min="9" max="9" width="31.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.8" spans="1:9">
-      <c r="A1" s="7" t="s">
+    <row r="1" ht="25.8" spans="1:11">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-    </row>
-    <row r="2" ht="17.4" spans="1:9">
-      <c r="A2" s="8" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" ht="17.4" spans="1:11">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="9">
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="11">
         <v>44747</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="9">
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="11">
         <v>44748</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6" t="s">
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6" t="s">
+      <c r="H4" s="12"/>
+      <c r="I4" s="12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="9">
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="11">
         <v>44749</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="9">
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="11">
         <v>44750</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6" t="s">
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" ht="28.8" spans="1:9">
-      <c r="A7" s="9">
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" ht="28.8" spans="1:11">
+      <c r="A7" s="11">
         <v>44751</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6" t="s">
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" ht="28.8" spans="1:9">
-      <c r="A8" s="9">
+      <c r="I7" s="12"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" ht="28.8" spans="1:11">
+      <c r="A8" s="11">
         <v>44752</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" ht="28.8" spans="1:9">
-      <c r="A9" s="9">
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" ht="28.8" spans="1:11">
+      <c r="A9" s="11">
         <v>44753</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6" t="s">
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" ht="28.8" spans="1:9">
-      <c r="A10" s="9">
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" ht="28.8" spans="1:11">
+      <c r="A10" s="11">
         <v>44754</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6" t="s">
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="6"/>
-    </row>
-    <row r="11" ht="43.2" spans="1:9">
-      <c r="A11" s="9">
+      <c r="I10" s="12"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" ht="43.2" spans="1:11">
+      <c r="A11" s="11">
         <v>44755</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="9">
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="11">
         <v>44756</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="9">
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="11">
         <v>44757</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="9">
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="11">
         <v>44758</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="9">
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="11">
         <v>44759</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-    </row>
-    <row r="16" ht="28.8" spans="1:9">
-      <c r="A16" s="9">
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" ht="28.8" spans="1:11">
+      <c r="A16" s="11">
         <v>44760</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-    </row>
-    <row r="17" ht="28.8" spans="1:9">
-      <c r="A17" s="9">
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" ht="28.8" spans="1:11">
+      <c r="A17" s="11">
         <v>44761</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6" t="s">
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-    </row>
-    <row r="18" ht="28.8" spans="1:9">
-      <c r="A18" s="9">
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" ht="28.8" spans="1:11">
+      <c r="A18" s="11">
         <v>44762</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-    </row>
-    <row r="19" ht="43.2" spans="1:9">
-      <c r="A19" s="9">
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" ht="43.2" spans="1:11">
+      <c r="A19" s="11">
         <v>44763</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6" t="s">
+      <c r="D19" s="12"/>
+      <c r="E19" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-    </row>
-    <row r="20" ht="28.8" spans="1:9">
-      <c r="A20" s="9">
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" ht="28.8" spans="1:11">
+      <c r="A20" s="11">
         <v>44764</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6" t="s">
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="21" ht="28.8" spans="1:9">
-      <c r="A21" s="9">
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" ht="28.8" spans="1:11">
+      <c r="A21" s="11">
         <v>44765</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6" t="s">
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="22" ht="43.2" spans="1:9">
-      <c r="A22" s="9">
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" ht="43.2" spans="1:11">
+      <c r="A22" s="11">
         <v>44766</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:9">
-      <c r="A23" s="9">
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:11">
+      <c r="A23" s="11">
         <v>44767</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-    </row>
-    <row r="24" ht="43.2" spans="1:9">
-      <c r="A24" s="9">
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" ht="43.2" spans="1:11">
+      <c r="A24" s="11">
         <v>44768</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6" t="s">
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="11" t="s">
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="25" ht="43.2" spans="1:9">
-      <c r="A25" s="9">
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" ht="43.2" spans="1:11">
+      <c r="A25" s="11">
         <v>44769</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6" t="s">
+      <c r="D25" s="12"/>
+      <c r="E25" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="11" t="s">
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="26" ht="43.2" spans="1:8">
-      <c r="A26" s="9">
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" ht="43.2" spans="1:11">
+      <c r="A26" s="11">
         <v>44770</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="G26" s="1"/>
+      <c r="H26" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="27" ht="43.2" spans="1:5">
-      <c r="A27" s="9">
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+    </row>
+    <row r="27" ht="43.2" spans="1:11">
+      <c r="A27" s="11">
         <v>44771</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D27" t="s">
+      <c r="C27" s="1"/>
+      <c r="D27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="12" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="9">
+      <c r="F27" s="12"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="11">
         <v>44772</v>
       </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="9">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="11">
         <v>44773</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="9">
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="11">
         <v>44774</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="E30" s="1"/>
+      <c r="F30" s="12" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="31" ht="43.2" spans="1:6">
-      <c r="A31" s="9">
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31" ht="43.2" spans="1:11">
+      <c r="A31" s="11">
         <v>44775</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="D31" s="1"/>
+      <c r="E31" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="12" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="32" ht="43.2" spans="1:2">
-      <c r="A32" s="9">
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32" ht="43.2" spans="1:11">
+      <c r="A32" s="11">
         <v>44776</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="33" ht="28.8" spans="1:3">
-      <c r="A33" s="9">
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+    </row>
+    <row r="33" ht="28.8" spans="1:11">
+      <c r="A33" s="11">
         <v>44777</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="34" ht="43.2" spans="1:8">
-      <c r="A34" s="9">
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+    </row>
+    <row r="34" ht="43.2" spans="1:11">
+      <c r="A34" s="11">
         <v>44778</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G34" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="9">
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="11">
         <v>44779</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="36" ht="28.8" spans="1:6">
-      <c r="A36" s="9">
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+    </row>
+    <row r="36" ht="28.8" spans="1:11">
+      <c r="A36" s="11">
         <v>44780</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="12" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="9">
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="11">
         <v>44781</v>
       </c>
-      <c r="B37" s="10"/>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="9">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="11">
         <v>44782</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="9">
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="11">
         <v>44783</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="9">
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="11">
         <v>44784</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="41" ht="43.2" spans="1:2">
-      <c r="A41" s="9">
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+    </row>
+    <row r="41" ht="43.2" spans="1:11">
+      <c r="A41" s="11">
         <v>44785</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="42" ht="28.8" spans="1:2">
-      <c r="A42" s="9">
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+    </row>
+    <row r="42" ht="28.8" spans="1:11">
+      <c r="A42" s="11">
         <v>44786</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="43" ht="43.2" spans="1:8">
-      <c r="A43" s="9">
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+    </row>
+    <row r="43" ht="43.2" spans="1:11">
+      <c r="A43" s="11">
         <v>44787</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="H43" t="s">
+      <c r="F43" s="12"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="44" ht="28.8" spans="1:8">
-      <c r="A44" s="9">
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+    </row>
+    <row r="44" ht="28.8" spans="1:11">
+      <c r="A44" s="11">
         <v>44788</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="H44" t="s">
+      <c r="F44" s="12"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="45" ht="28.8" spans="1:5">
-      <c r="A45" s="9">
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+    </row>
+    <row r="45" ht="28.8" spans="1:11">
+      <c r="A45" s="11">
         <v>44789</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="12" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="46" ht="43.2" spans="1:5">
-      <c r="A46" s="9">
+      <c r="F45" s="12"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+    </row>
+    <row r="46" ht="43.2" spans="1:11">
+      <c r="A46" s="11">
         <v>44790</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="D46" s="1"/>
+      <c r="E46" s="12" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="9">
+      <c r="F46" s="12"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="11">
         <v>44791</v>
       </c>
-      <c r="C47" t="s">
+      <c r="B47" s="1"/>
+      <c r="C47" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="12" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="9">
+      <c r="F47" s="12"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="11">
         <v>44792</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="49" ht="28.8" spans="1:8">
-      <c r="A49" s="9">
+      <c r="E48" s="1"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+    </row>
+    <row r="49" ht="28.8" spans="1:11">
+      <c r="A49" s="11">
         <v>44793</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H49" t="s">
+      <c r="E49" s="1"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="9">
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="11">
         <v>44794</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="H50" t="s">
+      <c r="E50" s="1"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="9">
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="11">
         <v>44795</v>
       </c>
-      <c r="C51" t="s">
+      <c r="B51" s="1"/>
+      <c r="C51" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="D51" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H51" t="s">
+      <c r="E51" s="1"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="9">
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+    </row>
+    <row r="52" ht="62" customHeight="1" spans="1:11">
+      <c r="A52" s="11">
         <v>44796</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="9">
+      <c r="B52" s="1"/>
+      <c r="C52" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+    </row>
+    <row r="53" ht="43.2" spans="1:11">
+      <c r="A53" s="11">
         <v>44797</v>
       </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="9">
+      <c r="B53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+    </row>
+    <row r="54" ht="43.2" spans="1:11">
+      <c r="A54" s="11">
         <v>44798</v>
       </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="9">
+      <c r="B54" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F54" s="12"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+    </row>
+    <row r="55" ht="28.8" spans="1:11">
+      <c r="A55" s="11">
         <v>44799</v>
       </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="9">
+      <c r="B55" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+    </row>
+    <row r="56" ht="28.8" spans="1:11">
+      <c r="A56" s="11">
         <v>44800</v>
       </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="9">
+      <c r="B56" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E56" s="1"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+    </row>
+    <row r="57" ht="43.2" spans="1:11">
+      <c r="A57" s="11">
         <v>44801</v>
       </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="9">
+      <c r="B57" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E57" s="1"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="11">
         <v>44802</v>
       </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="9">
+      <c r="B58" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="11">
         <v>44803</v>
       </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="9">
+      <c r="B59" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F59" s="12"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="11">
         <v>44804</v>
       </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="9">
+      <c r="B60" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="11">
         <v>44805</v>
       </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="9">
+      <c r="B61" s="1"/>
+      <c r="C61" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F61" s="12"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="11">
         <v>44806</v>
       </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="9">
+      <c r="B62" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F62" s="12"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="11">
         <v>44807</v>
       </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="9">
+      <c r="B63" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F63" s="12"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="11">
         <v>44808</v>
       </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="9">
+      <c r="B64" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="11">
         <v>44809</v>
       </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="9">
+      <c r="B65" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F65" s="12"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="11">
         <v>44810</v>
       </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="9">
+      <c r="B66" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" s="11">
         <v>44811</v>
       </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="9">
+      <c r="B67" s="1"/>
+      <c r="C67" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="11">
         <v>44812</v>
       </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="9">
+      <c r="B68" s="1"/>
+      <c r="C68" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="11">
         <v>44813</v>
       </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" s="9">
+      <c r="B69" s="1"/>
+      <c r="C69" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="11">
         <v>44814</v>
       </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="9">
+      <c r="B70" s="1"/>
+      <c r="C70" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="11">
         <v>44815</v>
       </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="9">
+      <c r="B71" s="1"/>
+      <c r="C71" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="11">
         <v>44816</v>
       </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" s="9">
+      <c r="B72" s="1"/>
+      <c r="C72" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="11">
         <v>44817</v>
       </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="9">
+      <c r="B73" s="1"/>
+      <c r="C73" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="11">
         <v>44818</v>
       </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="9">
+      <c r="B74" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E74" s="1"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="11">
         <v>44819</v>
       </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="9">
+      <c r="B75" s="1"/>
+      <c r="C75" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="11">
         <v>44820</v>
       </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="9">
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="11">
         <v>44821</v>
       </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" s="9">
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E77" s="1"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="11">
         <v>44822</v>
       </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" s="9">
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E78" s="1"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+    </row>
+    <row r="79" ht="28.8" spans="1:11">
+      <c r="A79" s="11">
         <v>44823</v>
       </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="9">
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E79" s="1"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+    </row>
+    <row r="80" ht="43.2" spans="1:11">
+      <c r="A80" s="11">
         <v>44824</v>
       </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="9">
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E80" s="1"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="11">
         <v>44825</v>
       </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="9">
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E81" s="1"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+    </row>
+    <row r="82" ht="28.8" spans="1:11">
+      <c r="A82" s="11">
         <v>44826</v>
       </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="9">
+      <c r="B82" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E82" s="1"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="11">
         <v>44827</v>
       </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="9">
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="11">
         <v>44828</v>
       </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="9">
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E84" s="1"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1"/>
+    </row>
+    <row r="85" ht="28.8" spans="1:11">
+      <c r="A85" s="11">
         <v>44829</v>
       </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="9">
+      <c r="B85" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E85" s="1"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+    </row>
+    <row r="86" ht="28.8" spans="1:11">
+      <c r="A86" s="11">
         <v>44830</v>
       </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="9">
+      <c r="B86" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E86" s="1"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+    </row>
+    <row r="87" ht="28.8" spans="1:11">
+      <c r="A87" s="11">
         <v>44831</v>
       </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="9">
+      <c r="B87" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E87" s="1"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1"/>
+    </row>
+    <row r="88" ht="28.8" spans="1:11">
+      <c r="A88" s="11">
         <v>44832</v>
       </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" s="9">
+      <c r="B88" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E88" s="1"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="11">
         <v>44833</v>
       </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" s="9">
+      <c r="B89" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E89" s="1"/>
+      <c r="F89" s="12"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
+      <c r="K89" s="1"/>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="11">
         <v>44834</v>
       </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" s="9">
+      <c r="B90" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F90" s="12"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="1"/>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="11">
         <v>44835</v>
       </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="9">
+      <c r="B91" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F91" s="12"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="11">
         <v>44836</v>
       </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="9">
+      <c r="B92" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F92" s="12"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="1"/>
+    </row>
+    <row r="93" ht="43.2" spans="1:11">
+      <c r="A93" s="11">
         <v>44837</v>
       </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" s="9">
+      <c r="B93" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F93" s="12"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+    </row>
+    <row r="94" ht="43.2" spans="1:11">
+      <c r="A94" s="11">
         <v>44838</v>
       </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="9">
+      <c r="B94" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F94" s="12"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
+      <c r="K94" s="1"/>
+    </row>
+    <row r="95" ht="43.2" spans="1:11">
+      <c r="A95" s="11">
         <v>44839</v>
       </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="9">
+      <c r="B95" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F95" s="12"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
+      <c r="K95" s="1"/>
+    </row>
+    <row r="96" ht="28.8" spans="1:11">
+      <c r="A96" s="11">
         <v>44840</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="9">
+      <c r="B96" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F96" s="12"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
+      <c r="K96" s="1"/>
+    </row>
+    <row r="97" ht="28.8" spans="1:11">
+      <c r="A97" s="11">
         <v>44841</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" s="9">
+      <c r="B97" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
+      <c r="K97" s="1"/>
+    </row>
+    <row r="98" ht="43.2" spans="1:11">
+      <c r="A98" s="11">
         <v>44842</v>
       </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" s="9">
+      <c r="B98" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F98" s="12"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+      <c r="J98" s="1"/>
+      <c r="K98" s="1"/>
+    </row>
+    <row r="99" ht="43.2" spans="1:11">
+      <c r="A99" s="11">
         <v>44843</v>
       </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="9">
+      <c r="B99" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E99" s="1"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1"/>
+      <c r="K99" s="1"/>
+    </row>
+    <row r="100" ht="28.8" spans="1:11">
+      <c r="A100" s="11">
         <v>44844</v>
       </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" s="9">
+      <c r="B100" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F100" s="12"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
+      <c r="K100" s="1"/>
+    </row>
+    <row r="101" ht="43.2" spans="1:11">
+      <c r="A101" s="11">
         <v>44845</v>
       </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" s="9">
+      <c r="B101" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F101" s="12"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+      <c r="K101" s="1"/>
+    </row>
+    <row r="102" ht="28.8" spans="1:11">
+      <c r="A102" s="11">
         <v>44846</v>
       </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="9">
+      <c r="B102" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F102" s="12"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1"/>
+      <c r="K102" s="1"/>
+    </row>
+    <row r="103" ht="28.8" spans="1:11">
+      <c r="A103" s="11">
         <v>44847</v>
       </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="9">
+      <c r="B103" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F103" s="12"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1"/>
+      <c r="K103" s="1"/>
+    </row>
+    <row r="104" ht="28.8" spans="1:11">
+      <c r="A104" s="11">
         <v>44848</v>
       </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="9">
+      <c r="B104" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
+      <c r="K104" s="1"/>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" s="11">
         <v>44849</v>
       </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" s="9">
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F105" s="12"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
+      <c r="K105" s="1"/>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" s="11">
         <v>44850</v>
       </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="9">
+      <c r="B106" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F106" s="12"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
+      <c r="K106" s="1"/>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107" s="11">
         <v>44851</v>
       </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" s="9">
+      <c r="C107" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F107" s="12"/>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1"/>
+      <c r="K107" s="1"/>
+    </row>
+    <row r="108" ht="28.8" spans="1:11">
+      <c r="A108" s="11">
         <v>44852</v>
       </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="9">
+      <c r="B108" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E108" s="1"/>
+      <c r="F108" s="12"/>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1"/>
+      <c r="K108" s="1"/>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109" s="11">
         <v>44853</v>
       </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="9">
+      <c r="B109" s="1"/>
+      <c r="C109" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F109" s="12"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1"/>
+      <c r="K109" s="1"/>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110" s="11">
         <v>44854</v>
       </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="9">
+      <c r="B110" s="1"/>
+      <c r="D110" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F110" s="12"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
+      <c r="K110" s="1"/>
+    </row>
+    <row r="111" ht="28.8" spans="1:11">
+      <c r="A111" s="11">
         <v>44855</v>
       </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" s="9">
+      <c r="B111" s="1"/>
+      <c r="C111" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F111" s="12"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
+      <c r="K111" s="1"/>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112" s="11">
         <v>44856</v>
       </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="9">
+      <c r="B112" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E112" s="1"/>
+      <c r="F112" s="12"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1"/>
+      <c r="K112" s="1"/>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113" s="11">
         <v>44857</v>
       </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" s="9">
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="12"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1"/>
+      <c r="K113" s="1"/>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="A114" s="11">
         <v>44858</v>
       </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" s="9">
+      <c r="B114" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E114" s="1"/>
+      <c r="F114" s="12"/>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1"/>
+      <c r="K114" s="1"/>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="A115" s="11">
         <v>44859</v>
       </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="9">
+      <c r="B115" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="C115" s="12"/>
+      <c r="D115" s="12"/>
+      <c r="E115" s="12"/>
+      <c r="F115" s="12"/>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1"/>
+      <c r="K115" s="1"/>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="A116" s="11">
         <v>44860</v>
       </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="9">
+      <c r="B116" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F116" s="12"/>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
+      <c r="I116" s="1"/>
+      <c r="J116" s="1"/>
+      <c r="K116" s="1"/>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="A117" s="11">
         <v>44861</v>
       </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="9">
+      <c r="B117" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+      <c r="E117" s="1"/>
+      <c r="F117" s="12"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
+      <c r="K117" s="1"/>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118" s="11">
         <v>44862</v>
       </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="9">
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F118" s="12"/>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1"/>
+      <c r="K118" s="1"/>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119" s="11">
         <v>44863</v>
       </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="9">
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F119" s="12"/>
+      <c r="G119" s="1"/>
+      <c r="H119" s="1"/>
+      <c r="I119" s="1"/>
+      <c r="J119" s="1"/>
+      <c r="K119" s="1"/>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120" s="11">
         <v>44864</v>
       </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="9">
+      <c r="B120" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F120" s="12"/>
+      <c r="G120" s="1"/>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1"/>
+      <c r="J120" s="1"/>
+      <c r="K120" s="1"/>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121" s="11">
         <v>44865</v>
       </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="9">
+      <c r="B121" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F121" s="12"/>
+      <c r="G121" s="1"/>
+      <c r="H121" s="1"/>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1"/>
+      <c r="K121" s="1"/>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="A122" s="11">
         <v>44866</v>
       </c>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="9">
+      <c r="B122" s="1"/>
+      <c r="C122" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F122" s="12"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1"/>
+      <c r="K122" s="1"/>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123" s="11">
         <v>44867</v>
       </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="9">
+      <c r="B123" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F123" s="12"/>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
+      <c r="J123" s="1"/>
+      <c r="K123" s="1"/>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124" s="11">
         <v>44868</v>
       </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="9">
+      <c r="B124" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D124" s="1"/>
+      <c r="E124" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F124" s="12"/>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+      <c r="J124" s="1"/>
+      <c r="K124" s="1"/>
+    </row>
+    <row r="125" spans="1:11">
+      <c r="A125" s="11">
         <v>44869</v>
       </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="9">
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
+      <c r="E125" s="1"/>
+      <c r="F125" s="12"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
+      <c r="J125" s="1"/>
+      <c r="K125" s="1"/>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" s="11">
         <v>44870</v>
       </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="9">
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+      <c r="E126" s="1"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1"/>
+      <c r="K126" s="1"/>
+    </row>
+    <row r="127" ht="28.8" spans="1:11">
+      <c r="A127" s="11">
         <v>44871</v>
       </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" s="9">
+      <c r="B127" s="1"/>
+      <c r="C127" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D127" s="1"/>
+      <c r="E127" s="1"/>
+      <c r="F127" s="12"/>
+      <c r="G127" s="1"/>
+      <c r="H127" s="1"/>
+      <c r="I127" s="1"/>
+      <c r="J127" s="1"/>
+      <c r="K127" s="1"/>
+    </row>
+    <row r="128" spans="1:11">
+      <c r="A128" s="11">
         <v>44872</v>
       </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="9">
+      <c r="B128" s="1"/>
+      <c r="C128" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F128" s="12"/>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1"/>
+      <c r="K128" s="1"/>
+    </row>
+    <row r="129" spans="1:11">
+      <c r="A129" s="11">
         <v>44873</v>
       </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="9">
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="12"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1"/>
+      <c r="K129" s="1"/>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="11">
         <v>44874</v>
       </c>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" s="9">
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
+      <c r="E130" s="1"/>
+      <c r="F130" s="12"/>
+      <c r="G130" s="1"/>
+      <c r="H130" s="1"/>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1"/>
+      <c r="K130" s="1"/>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="11">
         <v>44875</v>
       </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="9">
+      <c r="B131" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E131" s="1"/>
+      <c r="F131" s="12"/>
+      <c r="G131" s="1"/>
+      <c r="H131" s="1"/>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1"/>
+      <c r="K131" s="1"/>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="A132" s="11">
         <v>44876</v>
       </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" s="9">
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
+      <c r="E132" s="1"/>
+      <c r="F132" s="12"/>
+      <c r="G132" s="1"/>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1"/>
+      <c r="K132" s="1"/>
+    </row>
+    <row r="133" spans="1:11">
+      <c r="A133" s="11">
         <v>44877</v>
       </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" s="9">
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
+      <c r="E133" s="1"/>
+      <c r="F133" s="12"/>
+      <c r="G133" s="1"/>
+      <c r="H133" s="1"/>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1"/>
+      <c r="K133" s="1"/>
+    </row>
+    <row r="134" spans="1:11">
+      <c r="A134" s="11">
         <v>44878</v>
       </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" s="9">
+      <c r="B134" s="1"/>
+      <c r="C134" s="1"/>
+      <c r="D134" s="1"/>
+      <c r="E134" s="1"/>
+      <c r="F134" s="12"/>
+      <c r="G134" s="1"/>
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1"/>
+      <c r="K134" s="1"/>
+    </row>
+    <row r="135" spans="1:11">
+      <c r="A135" s="11">
         <v>44879</v>
       </c>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" s="9">
+      <c r="B135" s="1"/>
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
+      <c r="E135" s="1"/>
+      <c r="F135" s="12"/>
+      <c r="G135" s="1"/>
+      <c r="H135" s="1"/>
+      <c r="I135" s="1"/>
+      <c r="J135" s="1"/>
+      <c r="K135" s="1"/>
+    </row>
+    <row r="136" spans="1:11">
+      <c r="A136" s="11">
         <v>44880</v>
       </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" s="9">
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
+      <c r="E136" s="1"/>
+      <c r="F136" s="12"/>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1"/>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1"/>
+      <c r="K136" s="1"/>
+    </row>
+    <row r="137" spans="1:11">
+      <c r="A137" s="11">
         <v>44881</v>
       </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" s="9">
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1"/>
+      <c r="E137" s="1"/>
+      <c r="F137" s="12"/>
+      <c r="G137" s="1"/>
+      <c r="H137" s="1"/>
+      <c r="I137" s="1"/>
+      <c r="J137" s="1"/>
+      <c r="K137" s="1"/>
+    </row>
+    <row r="138" spans="1:11">
+      <c r="A138" s="11">
         <v>44882</v>
       </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="9">
+      <c r="B138" s="1"/>
+      <c r="C138" s="1"/>
+      <c r="D138" s="1"/>
+      <c r="E138" s="1"/>
+      <c r="F138" s="12"/>
+      <c r="G138" s="1"/>
+      <c r="H138" s="1"/>
+      <c r="I138" s="1"/>
+      <c r="J138" s="1"/>
+      <c r="K138" s="1"/>
+    </row>
+    <row r="139" spans="1:11">
+      <c r="A139" s="11">
         <v>44883</v>
       </c>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="9">
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1"/>
+      <c r="E139" s="1"/>
+      <c r="F139" s="12"/>
+      <c r="G139" s="1"/>
+      <c r="H139" s="1"/>
+      <c r="I139" s="1"/>
+      <c r="J139" s="1"/>
+      <c r="K139" s="1"/>
+    </row>
+    <row r="140" spans="1:11">
+      <c r="A140" s="11">
         <v>44884</v>
       </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" s="9">
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1"/>
+      <c r="E140" s="1"/>
+      <c r="F140" s="12"/>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1"/>
+      <c r="J140" s="1"/>
+      <c r="K140" s="1"/>
+    </row>
+    <row r="141" spans="1:11">
+      <c r="A141" s="11">
         <v>44885</v>
       </c>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="9">
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1"/>
+      <c r="E141" s="1"/>
+      <c r="F141" s="12"/>
+      <c r="G141" s="1"/>
+      <c r="H141" s="1"/>
+      <c r="I141" s="1"/>
+      <c r="J141" s="1"/>
+      <c r="K141" s="1"/>
+    </row>
+    <row r="142" spans="1:11">
+      <c r="A142" s="11">
         <v>44886</v>
       </c>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" s="9">
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
+      <c r="D142" s="1"/>
+      <c r="E142" s="1"/>
+      <c r="F142" s="12"/>
+      <c r="G142" s="1"/>
+      <c r="H142" s="1"/>
+      <c r="I142" s="1"/>
+      <c r="J142" s="1"/>
+      <c r="K142" s="1"/>
+    </row>
+    <row r="143" spans="1:11">
+      <c r="A143" s="11">
         <v>44887</v>
       </c>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" s="9">
+      <c r="B143" s="1"/>
+      <c r="C143" s="1"/>
+      <c r="D143" s="1"/>
+      <c r="E143" s="1"/>
+      <c r="F143" s="12"/>
+      <c r="G143" s="1"/>
+      <c r="H143" s="1"/>
+      <c r="I143" s="1"/>
+      <c r="J143" s="1"/>
+      <c r="K143" s="1"/>
+    </row>
+    <row r="144" spans="1:11">
+      <c r="A144" s="11">
         <v>44888</v>
       </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="9">
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
+      <c r="D144" s="1"/>
+      <c r="E144" s="1"/>
+      <c r="F144" s="12"/>
+      <c r="G144" s="1"/>
+      <c r="H144" s="1"/>
+      <c r="I144" s="1"/>
+      <c r="J144" s="1"/>
+      <c r="K144" s="1"/>
+    </row>
+    <row r="145" spans="1:11">
+      <c r="A145" s="11">
         <v>44889</v>
       </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="9">
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
+      <c r="D145" s="1"/>
+      <c r="E145" s="1"/>
+      <c r="F145" s="12"/>
+      <c r="G145" s="1"/>
+      <c r="H145" s="1"/>
+      <c r="I145" s="1"/>
+      <c r="J145" s="1"/>
+      <c r="K145" s="1"/>
+    </row>
+    <row r="146" spans="1:11">
+      <c r="A146" s="11">
         <v>44890</v>
       </c>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="9">
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
+      <c r="D146" s="1"/>
+      <c r="E146" s="1"/>
+      <c r="F146" s="12"/>
+      <c r="G146" s="1"/>
+      <c r="H146" s="1"/>
+      <c r="I146" s="1"/>
+      <c r="J146" s="1"/>
+      <c r="K146" s="1"/>
+    </row>
+    <row r="147" spans="1:11">
+      <c r="A147" s="11">
         <v>44891</v>
       </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="9">
+      <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1"/>
+      <c r="E147" s="1"/>
+      <c r="F147" s="12"/>
+      <c r="G147" s="1"/>
+      <c r="H147" s="1"/>
+      <c r="I147" s="1"/>
+      <c r="J147" s="1"/>
+      <c r="K147" s="1"/>
+    </row>
+    <row r="148" spans="1:11">
+      <c r="A148" s="11">
         <v>44892</v>
       </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="9">
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
+      <c r="E148" s="1"/>
+      <c r="F148" s="12"/>
+      <c r="G148" s="1"/>
+      <c r="H148" s="1"/>
+      <c r="I148" s="1"/>
+      <c r="J148" s="1"/>
+      <c r="K148" s="1"/>
+    </row>
+    <row r="149" spans="1:11">
+      <c r="A149" s="11">
         <v>44893</v>
       </c>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="9">
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
+      <c r="E149" s="1"/>
+      <c r="F149" s="12"/>
+      <c r="G149" s="1"/>
+      <c r="H149" s="1"/>
+      <c r="I149" s="1"/>
+      <c r="J149" s="1"/>
+      <c r="K149" s="1"/>
+    </row>
+    <row r="150" spans="1:11">
+      <c r="A150" s="11">
         <v>44894</v>
       </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="9">
+      <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
+      <c r="E150" s="1"/>
+      <c r="F150" s="12"/>
+      <c r="G150" s="1"/>
+      <c r="H150" s="1"/>
+      <c r="I150" s="1"/>
+      <c r="J150" s="1"/>
+      <c r="K150" s="1"/>
+    </row>
+    <row r="151" spans="1:11">
+      <c r="A151" s="11">
         <v>44895</v>
       </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" s="9">
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
+      <c r="D151" s="1"/>
+      <c r="E151" s="1"/>
+      <c r="F151" s="12"/>
+      <c r="G151" s="1"/>
+      <c r="H151" s="1"/>
+      <c r="I151" s="1"/>
+      <c r="J151" s="1"/>
+      <c r="K151" s="1"/>
+    </row>
+    <row r="152" spans="1:11">
+      <c r="A152" s="11">
         <v>44896</v>
       </c>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" s="9">
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1"/>
+      <c r="E152" s="1"/>
+      <c r="F152" s="12"/>
+      <c r="G152" s="1"/>
+      <c r="H152" s="1"/>
+      <c r="I152" s="1"/>
+      <c r="J152" s="1"/>
+      <c r="K152" s="1"/>
+    </row>
+    <row r="153" spans="1:11">
+      <c r="A153" s="11">
         <v>44897</v>
       </c>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" s="9">
+      <c r="B153" s="1"/>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1"/>
+      <c r="E153" s="1"/>
+      <c r="F153" s="12"/>
+      <c r="G153" s="1"/>
+      <c r="H153" s="1"/>
+      <c r="I153" s="1"/>
+      <c r="J153" s="1"/>
+      <c r="K153" s="1"/>
+    </row>
+    <row r="154" spans="1:11">
+      <c r="A154" s="11">
         <v>44898</v>
       </c>
-    </row>
-    <row r="155" spans="1:1">
-      <c r="A155" s="9">
+      <c r="B154" s="1"/>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
+      <c r="E154" s="1"/>
+      <c r="F154" s="12"/>
+      <c r="G154" s="1"/>
+      <c r="H154" s="1"/>
+      <c r="I154" s="1"/>
+      <c r="J154" s="1"/>
+      <c r="K154" s="1"/>
+    </row>
+    <row r="155" spans="1:11">
+      <c r="A155" s="11">
         <v>44899</v>
       </c>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" s="9">
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
+      <c r="E155" s="1"/>
+      <c r="F155" s="12"/>
+      <c r="G155" s="1"/>
+      <c r="H155" s="1"/>
+      <c r="I155" s="1"/>
+      <c r="J155" s="1"/>
+      <c r="K155" s="1"/>
+    </row>
+    <row r="156" spans="1:11">
+      <c r="A156" s="11">
         <v>44900</v>
       </c>
-    </row>
-    <row r="157" spans="1:1">
-      <c r="A157" s="9">
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1"/>
+      <c r="E156" s="1"/>
+      <c r="F156" s="12"/>
+      <c r="G156" s="1"/>
+      <c r="H156" s="1"/>
+      <c r="I156" s="1"/>
+      <c r="J156" s="1"/>
+      <c r="K156" s="1"/>
+    </row>
+    <row r="157" spans="1:11">
+      <c r="A157" s="11">
         <v>44901</v>
       </c>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" s="9">
+      <c r="B157" s="1"/>
+      <c r="C157" s="1"/>
+      <c r="D157" s="1"/>
+      <c r="E157" s="1"/>
+      <c r="F157" s="12"/>
+      <c r="G157" s="1"/>
+      <c r="H157" s="1"/>
+      <c r="I157" s="1"/>
+      <c r="J157" s="1"/>
+      <c r="K157" s="1"/>
+    </row>
+    <row r="158" spans="1:11">
+      <c r="A158" s="11">
         <v>44902</v>
       </c>
-    </row>
-    <row r="159" spans="1:1">
-      <c r="A159" s="9">
+      <c r="B158" s="1"/>
+      <c r="C158" s="1"/>
+      <c r="D158" s="1"/>
+      <c r="E158" s="1"/>
+      <c r="F158" s="12"/>
+      <c r="G158" s="1"/>
+      <c r="H158" s="1"/>
+      <c r="I158" s="1"/>
+      <c r="J158" s="1"/>
+      <c r="K158" s="1"/>
+    </row>
+    <row r="159" spans="1:11">
+      <c r="A159" s="11">
         <v>44903</v>
       </c>
-    </row>
-    <row r="160" spans="1:1">
-      <c r="A160" s="9">
+      <c r="B159" s="1"/>
+      <c r="C159" s="1"/>
+      <c r="D159" s="1"/>
+      <c r="E159" s="1"/>
+      <c r="F159" s="12"/>
+      <c r="G159" s="1"/>
+      <c r="H159" s="1"/>
+      <c r="I159" s="1"/>
+      <c r="J159" s="1"/>
+      <c r="K159" s="1"/>
+    </row>
+    <row r="160" spans="1:11">
+      <c r="A160" s="11">
         <v>44904</v>
       </c>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" s="9">
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
+      <c r="E160" s="1"/>
+      <c r="F160" s="12"/>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+      <c r="J160" s="1"/>
+      <c r="K160" s="1"/>
+    </row>
+    <row r="161" spans="1:11">
+      <c r="A161" s="11">
         <v>44905</v>
       </c>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" s="9">
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
+      <c r="E161" s="1"/>
+      <c r="F161" s="12"/>
+      <c r="G161" s="1"/>
+      <c r="H161" s="1"/>
+      <c r="I161" s="1"/>
+      <c r="J161" s="1"/>
+      <c r="K161" s="1"/>
+    </row>
+    <row r="162" spans="1:11">
+      <c r="A162" s="11">
         <v>44906</v>
       </c>
-    </row>
-    <row r="163" spans="1:1">
-      <c r="A163" s="9">
+      <c r="B162" s="1"/>
+      <c r="C162" s="1"/>
+      <c r="D162" s="1"/>
+      <c r="E162" s="1"/>
+      <c r="F162" s="12"/>
+      <c r="G162" s="1"/>
+      <c r="H162" s="1"/>
+      <c r="I162" s="1"/>
+      <c r="J162" s="1"/>
+      <c r="K162" s="1"/>
+    </row>
+    <row r="163" spans="1:11">
+      <c r="A163" s="11">
         <v>44907</v>
       </c>
-    </row>
-    <row r="164" spans="1:1">
-      <c r="A164" s="9">
+      <c r="B163" s="1"/>
+      <c r="C163" s="1"/>
+      <c r="D163" s="1"/>
+      <c r="E163" s="1"/>
+      <c r="F163" s="12"/>
+      <c r="G163" s="1"/>
+      <c r="H163" s="1"/>
+      <c r="I163" s="1"/>
+      <c r="J163" s="1"/>
+      <c r="K163" s="1"/>
+    </row>
+    <row r="164" spans="1:11">
+      <c r="A164" s="11">
         <v>44908</v>
       </c>
-    </row>
-    <row r="165" spans="1:1">
-      <c r="A165" s="9">
+      <c r="B164" s="1"/>
+      <c r="C164" s="1"/>
+      <c r="D164" s="1"/>
+      <c r="E164" s="1"/>
+      <c r="F164" s="12"/>
+      <c r="G164" s="1"/>
+      <c r="H164" s="1"/>
+      <c r="I164" s="1"/>
+      <c r="J164" s="1"/>
+      <c r="K164" s="1"/>
+    </row>
+    <row r="165" spans="1:11">
+      <c r="A165" s="11">
         <v>44909</v>
       </c>
-    </row>
-    <row r="166" spans="1:1">
-      <c r="A166" s="9">
+      <c r="B165" s="1"/>
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
+      <c r="E165" s="1"/>
+      <c r="F165" s="12"/>
+      <c r="G165" s="1"/>
+      <c r="H165" s="1"/>
+      <c r="I165" s="1"/>
+      <c r="J165" s="1"/>
+      <c r="K165" s="1"/>
+    </row>
+    <row r="166" spans="1:11">
+      <c r="A166" s="11">
         <v>44910</v>
       </c>
-    </row>
-    <row r="167" spans="1:1">
-      <c r="A167" s="9">
+      <c r="B166" s="1"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="1"/>
+      <c r="E166" s="1"/>
+      <c r="F166" s="12"/>
+      <c r="G166" s="1"/>
+      <c r="H166" s="1"/>
+      <c r="I166" s="1"/>
+      <c r="J166" s="1"/>
+      <c r="K166" s="1"/>
+    </row>
+    <row r="167" spans="1:11">
+      <c r="A167" s="11">
         <v>44911</v>
       </c>
-    </row>
-    <row r="168" spans="1:1">
-      <c r="A168" s="9">
+      <c r="B167" s="1"/>
+      <c r="C167" s="1"/>
+      <c r="D167" s="1"/>
+      <c r="E167" s="1"/>
+      <c r="F167" s="12"/>
+      <c r="G167" s="1"/>
+      <c r="H167" s="1"/>
+      <c r="I167" s="1"/>
+      <c r="J167" s="1"/>
+      <c r="K167" s="1"/>
+    </row>
+    <row r="168" spans="1:11">
+      <c r="A168" s="11">
         <v>44912</v>
       </c>
-    </row>
-    <row r="169" spans="1:1">
-      <c r="A169" s="9">
+      <c r="B168" s="1"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1"/>
+      <c r="E168" s="1"/>
+      <c r="F168" s="12"/>
+      <c r="G168" s="1"/>
+      <c r="H168" s="1"/>
+      <c r="I168" s="1"/>
+      <c r="J168" s="1"/>
+      <c r="K168" s="1"/>
+    </row>
+    <row r="169" spans="1:11">
+      <c r="A169" s="11">
         <v>44913</v>
       </c>
-    </row>
-    <row r="170" spans="1:1">
-      <c r="A170" s="9">
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
+      <c r="E169" s="1"/>
+      <c r="F169" s="12"/>
+      <c r="G169" s="1"/>
+      <c r="H169" s="1"/>
+      <c r="I169" s="1"/>
+      <c r="J169" s="1"/>
+      <c r="K169" s="1"/>
+    </row>
+    <row r="170" spans="1:11">
+      <c r="A170" s="11">
         <v>44914</v>
       </c>
-    </row>
-    <row r="171" spans="1:1">
-      <c r="A171" s="9">
+      <c r="B170" s="1"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
+      <c r="E170" s="1"/>
+      <c r="F170" s="12"/>
+      <c r="G170" s="1"/>
+      <c r="H170" s="1"/>
+      <c r="I170" s="1"/>
+      <c r="J170" s="1"/>
+      <c r="K170" s="1"/>
+    </row>
+    <row r="171" spans="1:11">
+      <c r="A171" s="11">
         <v>44915</v>
       </c>
-    </row>
-    <row r="172" spans="1:1">
-      <c r="A172" s="9">
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
+      <c r="E171" s="1"/>
+      <c r="F171" s="12"/>
+      <c r="G171" s="1"/>
+      <c r="H171" s="1"/>
+      <c r="I171" s="1"/>
+      <c r="J171" s="1"/>
+      <c r="K171" s="1"/>
+    </row>
+    <row r="172" spans="1:11">
+      <c r="A172" s="11">
         <v>44916</v>
       </c>
-    </row>
-    <row r="173" spans="1:1">
-      <c r="A173" s="9">
+      <c r="B172" s="1"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
+      <c r="E172" s="1"/>
+      <c r="F172" s="12"/>
+      <c r="G172" s="1"/>
+      <c r="H172" s="1"/>
+      <c r="I172" s="1"/>
+      <c r="J172" s="1"/>
+      <c r="K172" s="1"/>
+    </row>
+    <row r="173" spans="1:11">
+      <c r="A173" s="11">
         <v>44917</v>
       </c>
-    </row>
-    <row r="174" spans="1:1">
-      <c r="A174" s="9">
+      <c r="B173" s="1"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
+      <c r="E173" s="1"/>
+      <c r="F173" s="12"/>
+      <c r="G173" s="1"/>
+      <c r="H173" s="1"/>
+      <c r="I173" s="1"/>
+      <c r="J173" s="1"/>
+      <c r="K173" s="1"/>
+    </row>
+    <row r="174" spans="1:11">
+      <c r="A174" s="11">
         <v>44918</v>
       </c>
-    </row>
-    <row r="175" spans="1:1">
-      <c r="A175" s="9">
+      <c r="B174" s="1"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="1"/>
+      <c r="E174" s="1"/>
+      <c r="F174" s="12"/>
+      <c r="G174" s="1"/>
+      <c r="H174" s="1"/>
+      <c r="I174" s="1"/>
+      <c r="J174" s="1"/>
+      <c r="K174" s="1"/>
+    </row>
+    <row r="175" spans="1:11">
+      <c r="A175" s="11">
         <v>44919</v>
       </c>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="1"/>
+      <c r="E175" s="1"/>
+      <c r="F175" s="12"/>
+      <c r="G175" s="1"/>
+      <c r="H175" s="1"/>
+      <c r="I175" s="1"/>
+      <c r="J175" s="1"/>
+      <c r="K175" s="1"/>
     </row>
     <row r="176" spans="1:1">
-      <c r="A176" s="9">
+      <c r="A176" s="13">
         <v>44920</v>
       </c>
     </row>
     <row r="177" spans="1:1">
-      <c r="A177" s="9">
+      <c r="A177" s="13">
         <v>44921</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B115:E115"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2986,148 +5371,146 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+        <v>256</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>114</v>
+        <v>258</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C3" s="1"/>
+        <v>260</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" spans="2:3">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+        <v>262</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B6" t="s">
-        <v>120</v>
+        <v>263</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>122</v>
+        <v>265</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>124</v>
+        <v>267</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>269</v>
       </c>
       <c r="B11" t="s">
-        <v>126</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>271</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>273</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>131</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>132</v>
+        <v>276</v>
       </c>
       <c r="B24" t="s">
-        <v>133</v>
+        <v>277</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>134</v>
+        <v>278</v>
       </c>
       <c r="B25" t="s">
-        <v>135</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>136</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>137</v>
+        <v>280</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="29" spans="3:3">
-      <c r="C29" s="3"/>
+      <c r="C29" s="5"/>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>138</v>
+        <v>282</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="4" t="s">
-        <v>139</v>
+      <c r="A31" s="6" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="4" t="s">
-        <v>140</v>
+      <c r="A32" s="6" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="4" t="s">
-        <v>141</v>
+      <c r="A33" s="6" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1" spans="1:1">
-      <c r="A35" s="5" t="s">
-        <v>142</v>
+      <c r="A35" s="7" t="s">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -3135,9 +5518,8 @@
     <hyperlink ref="B2" r:id="rId1" display="https://www.bilibili.com/video/BV1Gt4y1H7PN"/>
     <hyperlink ref="B1" r:id="rId2" display="https://www.bilibili.com/video/BV17L4y1w7wY"/>
     <hyperlink ref="B26" r:id="rId3" display="https://zhuanlan.zhihu.com/p/489936535"/>
-    <hyperlink ref="B7" r:id="rId4" display="https://www.bilibili.com/video/BV1XG4y1e78a"/>
-    <hyperlink ref="B5" r:id="rId5" display="https://www.bilibili.com/video/BV1GN4y1T7o6"/>
-    <hyperlink ref="B9" r:id="rId6" display="https://www.bilibili.com/video/BV1jY4y1i7qT" tooltip="https://www.bilibili.com/video/BV1jY4y1i7qT"/>
+    <hyperlink ref="B9" r:id="rId4" display="https://www.bilibili.com/video/BV1jY4y1i7qT" tooltip="https://www.bilibili.com/video/BV1jY4y1i7qT"/>
+    <hyperlink ref="B6" r:id="rId5" display="https://www.bilibili.com/video/BV1Ze4y1f7B6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3147,9 +5529,75 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="78.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="65.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="40.8888888888889" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30.6" spans="1:3">
+      <c r="A1" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B1" s="2">
+        <v>660</v>
+      </c>
+      <c r="C1" s="2">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <cols>
+    <col min="4" max="4" width="102" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="2" ht="28.8" spans="1:4">
+      <c r="A2">
+        <v>2019</v>
+      </c>
+      <c r="B2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
